--- a/outputs/analysiss.xlsx
+++ b/outputs/analysiss.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="not in the list cars" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-03-2024@2134" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08-05-2024_@_17_56" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Voyah Free</t>
+          <t>Solaris SH</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeekr 001</t>
+          <t>Geely Belgee X50</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zeekr 009</t>
+          <t>Haval Jolion 2WD</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,187 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Haval Jolion 4WD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Changan UNI-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Geely Emgrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gac GS8 II</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Geely Atlas NEW Promo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Geely Emgrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Belgee X50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hyundai Tucson IV AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Geely Atlas NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Voyah Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zeekr 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zeekr 009</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Changan  UNI-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Changan CS 55 PLUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Changan UNI-T</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Changan EADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Jaguar XE ВК49865</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Zeekr 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lixang Li 9</t>
         </is>
       </c>
     </row>
@@ -544,27 +724,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RENT-MOTORS-05-03-24</t>
+          <t>RENT-MOTORS-08-05-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>REX-RENT-05-03-24</t>
+          <t>REX-RENT-08-05-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>A-ARENDA-05-03-24</t>
+          <t>A-ARENDA-08-05-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ALMAK-05-03-24</t>
+          <t>ALMAK-08-05-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>STORLET-05-03-24</t>
+          <t>STORLET-08-05-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -599,11 +779,7 @@
           <t>Volkswagen Polo V</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Renault Logan</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -620,23 +796,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2238.9</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1750</v>
-      </c>
+        <v>2634</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1750</v>
+        <v>2634</v>
       </c>
       <c r="J3" t="n">
-        <v>488.9000000000001</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>21.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -647,23 +821,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2127.55</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1750</v>
-      </c>
+        <v>2503</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1750</v>
+        <v>2503</v>
       </c>
       <c r="J4" t="n">
-        <v>377.5499999999997</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>17.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -674,23 +846,21 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2015.35</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1500</v>
-      </c>
+        <v>2371</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1500</v>
+        <v>2371</v>
       </c>
       <c r="J5" t="n">
-        <v>515.3499999999999</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>25.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -701,23 +871,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1858.95</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1500</v>
-      </c>
+        <v>2187</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1500</v>
+        <v>2187</v>
       </c>
       <c r="J6" t="n">
-        <v>358.95</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>19.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -728,23 +896,21 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1746.75</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1500</v>
-      </c>
+        <v>2055</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1500</v>
+        <v>2055</v>
       </c>
       <c r="J7" t="n">
-        <v>246.75</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>14.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -755,23 +921,21 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1679.6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1450</v>
-      </c>
+        <v>1976</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1450</v>
+        <v>1976</v>
       </c>
       <c r="J8" t="n">
-        <v>229.5999999999999</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>13.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -803,7 +967,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2798.2</v>
+        <v>3292</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -811,7 +975,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>2798.2</v>
+        <v>3292</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -828,7 +992,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2658.8</v>
+        <v>3128</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -836,7 +1000,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>2658.8</v>
+        <v>3128</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -853,7 +1017,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2518.55</v>
+        <v>2963</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -861,7 +1025,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>2518.55</v>
+        <v>2963</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -878,7 +1042,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2323.05</v>
+        <v>2733</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -886,7 +1050,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>2323.05</v>
+        <v>2733</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -903,7 +1067,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2182.8</v>
+        <v>2568</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -911,7 +1075,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>2182.8</v>
+        <v>2568</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -928,7 +1092,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2098.65</v>
+        <v>2469</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -936,7 +1100,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>2098.65</v>
+        <v>2469</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1141,23 +1305,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3280.15</v>
+        <v>3859</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>3470</v>
+        <v>3770</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>3280.15</v>
+        <v>3770</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="25">
@@ -1168,23 +1332,23 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3116.95</v>
+        <v>3667</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>3270</v>
+        <v>3570</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>3116.95</v>
+        <v>3570</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="26">
@@ -1195,23 +1359,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2952.9</v>
+        <v>3474</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>2970</v>
+        <v>3270</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>2952.9</v>
+        <v>3270</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="27">
@@ -1222,17 +1386,17 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2624.8</v>
+        <v>3088</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>2970</v>
+        <v>3270</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>2624.8</v>
+        <v>3088</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1249,17 +1413,17 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2296.7</v>
+        <v>2702</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>2870</v>
+        <v>3070</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>2296.7</v>
+        <v>2702</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1276,17 +1440,17 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2296.7</v>
+        <v>2702</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>2870</v>
+        <v>3070</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>2296.7</v>
+        <v>2702</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1328,7 +1492,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2288.8</v>
+        <v>2861</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -1336,7 +1500,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>2288.8</v>
+        <v>2861</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1353,7 +1517,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2174.4</v>
+        <v>2718</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -1361,7 +1525,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>2174.4</v>
+        <v>2718</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1378,7 +1542,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2060</v>
+        <v>2575</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -1386,7 +1550,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>2060</v>
+        <v>2575</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1403,7 +1567,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1900</v>
+        <v>2375</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -1411,7 +1575,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>1900</v>
+        <v>2375</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1428,7 +1592,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1785.6</v>
+        <v>2232</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -1436,7 +1600,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>1785.6</v>
+        <v>2232</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1453,7 +1617,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1716.8</v>
+        <v>2146</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -1461,7 +1625,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>1716.8</v>
+        <v>2146</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1523,19 +1687,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2860.8</v>
+        <v>3576</v>
       </c>
       <c r="D38" t="n">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="E38" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="F38" t="n">
-        <v>3150</v>
+        <v>3330</v>
       </c>
       <c r="G38" t="n">
-        <v>2570</v>
+        <v>2770</v>
       </c>
       <c r="H38" t="n">
         <v>2000</v>
@@ -1544,10 +1708,10 @@
         <v>2000</v>
       </c>
       <c r="J38" t="n">
-        <v>860.8000000000002</v>
+        <v>1576</v>
       </c>
       <c r="K38" t="n">
-        <v>30.09</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="39">
@@ -1558,19 +1722,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2718.4</v>
+        <v>3398</v>
       </c>
       <c r="D39" t="n">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="E39" t="n">
-        <v>2816.67</v>
+        <v>3100</v>
       </c>
       <c r="F39" t="n">
-        <v>2830</v>
+        <v>2990</v>
       </c>
       <c r="G39" t="n">
-        <v>2470</v>
+        <v>2570</v>
       </c>
       <c r="H39" t="n">
         <v>2000</v>
@@ -1579,10 +1743,10 @@
         <v>2000</v>
       </c>
       <c r="J39" t="n">
-        <v>718.4000000000001</v>
+        <v>1398</v>
       </c>
       <c r="K39" t="n">
-        <v>26.43</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="40">
@@ -1593,19 +1757,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2575.2</v>
+        <v>3219</v>
       </c>
       <c r="D40" t="n">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="E40" t="n">
-        <v>2321.43</v>
+        <v>2900</v>
       </c>
       <c r="F40" t="n">
-        <v>2710</v>
+        <v>2860</v>
       </c>
       <c r="G40" t="n">
-        <v>2270</v>
+        <v>2470</v>
       </c>
       <c r="H40" t="n">
         <v>1800</v>
@@ -1614,10 +1778,10 @@
         <v>1800</v>
       </c>
       <c r="J40" t="n">
-        <v>775.2000000000003</v>
+        <v>1419</v>
       </c>
       <c r="K40" t="n">
-        <v>30.1</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="41">
@@ -1628,19 +1792,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2375.2</v>
+        <v>2969</v>
       </c>
       <c r="D41" t="n">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="E41" t="n">
-        <v>2285.71</v>
+        <v>2600</v>
       </c>
       <c r="F41" t="n">
-        <v>2710</v>
+        <v>2860</v>
       </c>
       <c r="G41" t="n">
-        <v>2270</v>
+        <v>2470</v>
       </c>
       <c r="H41" t="n">
         <v>1800</v>
@@ -1649,10 +1813,10 @@
         <v>1800</v>
       </c>
       <c r="J41" t="n">
-        <v>575.2000000000003</v>
+        <v>1169</v>
       </c>
       <c r="K41" t="n">
-        <v>24.22</v>
+        <v>39.37</v>
       </c>
     </row>
     <row r="42">
@@ -1663,19 +1827,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2232</v>
+        <v>2790</v>
       </c>
       <c r="D42" t="n">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="E42" t="n">
-        <v>2273.81</v>
+        <v>2500</v>
       </c>
       <c r="F42" t="n">
-        <v>2520</v>
+        <v>2660</v>
       </c>
       <c r="G42" t="n">
-        <v>2170</v>
+        <v>2270</v>
       </c>
       <c r="H42" t="n">
         <v>1500</v>
@@ -1684,10 +1848,10 @@
         <v>1500</v>
       </c>
       <c r="J42" t="n">
-        <v>732</v>
+        <v>1290</v>
       </c>
       <c r="K42" t="n">
-        <v>32.8</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="43">
@@ -1698,19 +1862,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2145.6</v>
+        <v>2682</v>
       </c>
       <c r="D43" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="E43" t="n">
-        <v>2216.67</v>
+        <v>2420</v>
       </c>
       <c r="F43" t="n">
-        <v>2424.33</v>
+        <v>2660</v>
       </c>
       <c r="G43" t="n">
-        <v>2170</v>
+        <v>2270</v>
       </c>
       <c r="H43" t="n">
         <v>1500</v>
@@ -1719,10 +1883,10 @@
         <v>1500</v>
       </c>
       <c r="J43" t="n">
-        <v>645.5999999999999</v>
+        <v>1182</v>
       </c>
       <c r="K43" t="n">
-        <v>30.09</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="44">
@@ -1758,7 +1922,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1983</v>
+        <v>3305</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -1766,7 +1930,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>1983</v>
+        <v>3305</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -1783,7 +1947,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1884</v>
+        <v>3140</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -1791,7 +1955,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>1884</v>
+        <v>3140</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -1808,7 +1972,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1785</v>
+        <v>2975</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -1816,7 +1980,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>1785</v>
+        <v>2975</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -1833,7 +1997,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1586.4</v>
+        <v>2644</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -1841,7 +2005,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>1586.4</v>
+        <v>2644</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -1858,7 +2022,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1388.4</v>
+        <v>2314</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -1866,7 +2030,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>1388.4</v>
+        <v>2314</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -1883,7 +2047,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1388.4</v>
+        <v>2314</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -1891,7 +2055,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>1388.4</v>
+        <v>2314</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -1916,11 +2080,7 @@
           <t>Volkswagen Polo VI; Skoda Rapid II</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Renault Logan.1</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -1945,15 +2105,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2478.6</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1950</v>
-      </c>
+        <v>4131</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>2570</v>
+        <v>2770</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
@@ -1962,10 +2120,10 @@
         <v>1800</v>
       </c>
       <c r="J52" t="n">
-        <v>678.5999999999999</v>
+        <v>2331</v>
       </c>
       <c r="K52" t="n">
-        <v>27.38</v>
+        <v>56.43</v>
       </c>
     </row>
     <row r="53">
@@ -1976,15 +2134,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2355</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1950</v>
-      </c>
+        <v>3925</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>2470</v>
+        <v>2570</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
@@ -1993,10 +2149,10 @@
         <v>1800</v>
       </c>
       <c r="J53" t="n">
-        <v>555</v>
+        <v>2125</v>
       </c>
       <c r="K53" t="n">
-        <v>23.57</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="54">
@@ -2007,15 +2163,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2230.8</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1700</v>
-      </c>
+        <v>3718</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>2270</v>
+        <v>2470</v>
       </c>
       <c r="H54" t="n">
         <v>1600</v>
@@ -2024,10 +2178,10 @@
         <v>1600</v>
       </c>
       <c r="J54" t="n">
-        <v>630.7999999999997</v>
+        <v>2118</v>
       </c>
       <c r="K54" t="n">
-        <v>28.28</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="55">
@@ -2038,15 +2192,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1983</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1700</v>
-      </c>
+        <v>3305</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>2270</v>
+        <v>2470</v>
       </c>
       <c r="H55" t="n">
         <v>1600</v>
@@ -2055,10 +2207,10 @@
         <v>1600</v>
       </c>
       <c r="J55" t="n">
-        <v>383</v>
+        <v>1705</v>
       </c>
       <c r="K55" t="n">
-        <v>19.31</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="56">
@@ -2069,15 +2221,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1735.2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1700</v>
-      </c>
+        <v>2892</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>2170</v>
+        <v>2270</v>
       </c>
       <c r="H56" t="n">
         <v>1400</v>
@@ -2086,10 +2236,10 @@
         <v>1400</v>
       </c>
       <c r="J56" t="n">
-        <v>335.2</v>
+        <v>1492</v>
       </c>
       <c r="K56" t="n">
-        <v>19.32</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="57">
@@ -2100,15 +2250,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1735.2</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1600</v>
-      </c>
+        <v>2892</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>2170</v>
+        <v>2270</v>
       </c>
       <c r="H57" t="n">
         <v>1400</v>
@@ -2117,10 +2265,10 @@
         <v>1400</v>
       </c>
       <c r="J57" t="n">
-        <v>335.2</v>
+        <v>1492</v>
       </c>
       <c r="K57" t="n">
-        <v>19.32</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="58">
@@ -2149,7 +2297,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Nissan Almera</t>
+          <t>Skoda Octavia</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -2164,7 +2312,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3136.5</v>
+        <v>3690</v>
       </c>
       <c r="D59" t="n">
         <v>3000</v>
@@ -2173,16 +2321,16 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="I59" t="n">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="J59" t="n">
-        <v>1336.5</v>
+        <v>690</v>
       </c>
       <c r="K59" t="n">
-        <v>42.61</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="60">
@@ -2193,7 +2341,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2980.1</v>
+        <v>3506</v>
       </c>
       <c r="D60" t="n">
         <v>3000</v>
@@ -2202,16 +2350,16 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="I60" t="n">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="J60" t="n">
-        <v>1180.1</v>
+        <v>506</v>
       </c>
       <c r="K60" t="n">
-        <v>39.6</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="61">
@@ -2222,7 +2370,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2822.85</v>
+        <v>3321</v>
       </c>
       <c r="D61" t="n">
         <v>2600</v>
@@ -2231,16 +2379,16 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1600</v>
+        <v>2900</v>
       </c>
       <c r="I61" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="J61" t="n">
-        <v>1222.85</v>
+        <v>721</v>
       </c>
       <c r="K61" t="n">
-        <v>43.32</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="62">
@@ -2251,7 +2399,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2509.2</v>
+        <v>2952</v>
       </c>
       <c r="D62" t="n">
         <v>2600</v>
@@ -2260,16 +2408,16 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>1600</v>
+        <v>2900</v>
       </c>
       <c r="I62" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="J62" t="n">
-        <v>909.1999999999998</v>
+        <v>352</v>
       </c>
       <c r="K62" t="n">
-        <v>36.23</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="63">
@@ -2280,7 +2428,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2195.55</v>
+        <v>2583</v>
       </c>
       <c r="D63" t="n">
         <v>2600</v>
@@ -2289,16 +2437,16 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="I63" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="J63" t="n">
-        <v>995.5499999999997</v>
+        <v>83</v>
       </c>
       <c r="K63" t="n">
-        <v>45.34</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="64">
@@ -2309,25 +2457,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2195.55</v>
+        <v>2583</v>
       </c>
       <c r="D64" t="n">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="I64" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="J64" t="n">
-        <v>995.5499999999997</v>
+        <v>183</v>
       </c>
       <c r="K64" t="n">
-        <v>45.34</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="65">
@@ -2347,16 +2495,12 @@
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Changan UNI-V</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Chevrolet Cruze sedan</t>
+          <t>Kia Ceed</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -2371,25 +2515,23 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3689.85</v>
+        <v>4341</v>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="n">
-        <v>6055</v>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I66" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="J66" t="n">
-        <v>1589.85</v>
+        <v>2141</v>
       </c>
       <c r="K66" t="n">
-        <v>43.09</v>
+        <v>49.32</v>
       </c>
     </row>
     <row r="67">
@@ -2400,25 +2542,23 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3505.4</v>
+        <v>4124</v>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="n">
-        <v>5721.67</v>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I67" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="J67" t="n">
-        <v>1405.4</v>
+        <v>1924</v>
       </c>
       <c r="K67" t="n">
-        <v>40.09</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="68">
@@ -2429,25 +2569,23 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3320.95</v>
+        <v>3907</v>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="n">
-        <v>5076.43</v>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="I68" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="J68" t="n">
-        <v>1420.95</v>
+        <v>1807</v>
       </c>
       <c r="K68" t="n">
-        <v>42.79</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="69">
@@ -2458,25 +2596,23 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2952.05</v>
+        <v>3473</v>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="n">
-        <v>5040.71</v>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="I69" t="n">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="J69" t="n">
-        <v>1052.05</v>
+        <v>1373</v>
       </c>
       <c r="K69" t="n">
-        <v>35.64</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="70">
@@ -2487,25 +2623,23 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2583.15</v>
+        <v>3039</v>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="n">
-        <v>5028.81</v>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I70" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="J70" t="n">
-        <v>1083.15</v>
+        <v>1039</v>
       </c>
       <c r="K70" t="n">
-        <v>41.93</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="71">
@@ -2516,25 +2650,23 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2583.15</v>
+        <v>3039</v>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="n">
-        <v>4471.67</v>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I71" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="J71" t="n">
-        <v>1083.15</v>
+        <v>1039</v>
       </c>
       <c r="K71" t="n">
-        <v>41.93</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="72">
@@ -2590,19 +2722,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4250.849999999999</v>
+        <v>5001</v>
       </c>
       <c r="D73" t="n">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="E73" t="n">
-        <v>6308</v>
+        <v>9100</v>
       </c>
       <c r="F73" t="n">
-        <v>3510</v>
+        <v>3900</v>
       </c>
       <c r="G73" t="n">
-        <v>3970</v>
+        <v>4370</v>
       </c>
       <c r="H73" t="n">
         <v>2500</v>
@@ -2611,10 +2743,10 @@
         <v>2500</v>
       </c>
       <c r="J73" t="n">
-        <v>1750.849999999999</v>
+        <v>2501</v>
       </c>
       <c r="K73" t="n">
-        <v>41.19</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="74">
@@ -2625,19 +2757,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4038.35</v>
+        <v>4751</v>
       </c>
       <c r="D74" t="n">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="E74" t="n">
-        <v>5974.33</v>
+        <v>8100</v>
       </c>
       <c r="F74" t="n">
-        <v>3510</v>
+        <v>3710</v>
       </c>
       <c r="G74" t="n">
-        <v>3670</v>
+        <v>4070</v>
       </c>
       <c r="H74" t="n">
         <v>2500</v>
@@ -2646,10 +2778,10 @@
         <v>2500</v>
       </c>
       <c r="J74" t="n">
-        <v>1538.35</v>
+        <v>2251</v>
       </c>
       <c r="K74" t="n">
-        <v>38.09</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="75">
@@ -2660,19 +2792,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3825.85</v>
+        <v>4501</v>
       </c>
       <c r="D75" t="n">
-        <v>3200</v>
+        <v>3700</v>
       </c>
       <c r="E75" t="n">
-        <v>5304</v>
+        <v>6250</v>
       </c>
       <c r="F75" t="n">
         <v>3510</v>
       </c>
       <c r="G75" t="n">
-        <v>3370</v>
+        <v>3670</v>
       </c>
       <c r="H75" t="n">
         <v>2400</v>
@@ -2681,10 +2813,10 @@
         <v>2400</v>
       </c>
       <c r="J75" t="n">
-        <v>1425.85</v>
+        <v>2101</v>
       </c>
       <c r="K75" t="n">
-        <v>37.27</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="76">
@@ -2695,19 +2827,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3400.85</v>
+        <v>4001</v>
       </c>
       <c r="D76" t="n">
-        <v>3200</v>
+        <v>3700</v>
       </c>
       <c r="E76" t="n">
-        <v>5268.21</v>
+        <v>5500</v>
       </c>
       <c r="F76" t="n">
         <v>3510</v>
       </c>
       <c r="G76" t="n">
-        <v>3370</v>
+        <v>3670</v>
       </c>
       <c r="H76" t="n">
         <v>2400</v>
@@ -2716,10 +2848,10 @@
         <v>2400</v>
       </c>
       <c r="J76" t="n">
-        <v>1000.85</v>
+        <v>1601</v>
       </c>
       <c r="K76" t="n">
-        <v>29.43</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="77">
@@ -2730,19 +2862,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2975.85</v>
+        <v>3501</v>
       </c>
       <c r="D77" t="n">
-        <v>3200</v>
+        <v>3700</v>
       </c>
       <c r="E77" t="n">
-        <v>5256.33</v>
+        <v>5300</v>
       </c>
       <c r="F77" t="n">
-        <v>3320</v>
+        <v>3347.62</v>
       </c>
       <c r="G77" t="n">
-        <v>3170</v>
+        <v>3570</v>
       </c>
       <c r="H77" t="n">
         <v>1900</v>
@@ -2751,10 +2883,10 @@
         <v>1900</v>
       </c>
       <c r="J77" t="n">
-        <v>1075.85</v>
+        <v>1601</v>
       </c>
       <c r="K77" t="n">
-        <v>36.15</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="78">
@@ -2765,19 +2897,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2975.85</v>
+        <v>3501</v>
       </c>
       <c r="D78" t="n">
-        <v>2800</v>
+        <v>3300</v>
       </c>
       <c r="E78" t="n">
-        <v>4674.17</v>
+        <v>4800</v>
       </c>
       <c r="F78" t="n">
-        <v>3686.33</v>
+        <v>3426.33</v>
       </c>
       <c r="G78" t="n">
-        <v>3170</v>
+        <v>3570</v>
       </c>
       <c r="H78" t="n">
         <v>1900</v>
@@ -2786,10 +2918,10 @@
         <v>1900</v>
       </c>
       <c r="J78" t="n">
-        <v>1075.85</v>
+        <v>1601</v>
       </c>
       <c r="K78" t="n">
-        <v>36.15</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="79">
@@ -2821,7 +2953,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4722.599999999999</v>
+        <v>5556</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -2829,7 +2961,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>4722.599999999999</v>
+        <v>5556</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -2846,7 +2978,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4487.15</v>
+        <v>5279</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -2854,7 +2986,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>4487.15</v>
+        <v>5279</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -2871,7 +3003,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4250.849999999999</v>
+        <v>5001</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -2879,7 +3011,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>4250.849999999999</v>
+        <v>5001</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -2896,7 +3028,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3778.25</v>
+        <v>4445</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -2904,7 +3036,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>3778.25</v>
+        <v>4445</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -2921,7 +3053,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3306.5</v>
+        <v>3890</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -2929,7 +3061,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>3306.5</v>
+        <v>3890</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -2946,7 +3078,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3306.5</v>
+        <v>3890</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -2954,7 +3086,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>3306.5</v>
+        <v>3890</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -2979,16 +3111,12 @@
           <t>Hyundai CRETA I</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Hyundai Creta</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hyundai Creta AT Promo</t>
+          <t>Hyundai Creta AT</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3008,15 +3136,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3231.2</v>
-      </c>
-      <c r="D87" t="n">
-        <v>3300</v>
-      </c>
+        <v>4039</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>2970</v>
+        <v>3970</v>
       </c>
       <c r="H87" t="n">
         <v>2200</v>
@@ -3025,10 +3151,10 @@
         <v>2200</v>
       </c>
       <c r="J87" t="n">
-        <v>1031.2</v>
+        <v>1839</v>
       </c>
       <c r="K87" t="n">
-        <v>31.91</v>
+        <v>45.53</v>
       </c>
     </row>
     <row r="88">
@@ -3039,15 +3165,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3070.4</v>
-      </c>
-      <c r="D88" t="n">
-        <v>3300</v>
-      </c>
+        <v>3838</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>2770</v>
+        <v>3770</v>
       </c>
       <c r="H88" t="n">
         <v>2200</v>
@@ -3056,10 +3180,10 @@
         <v>2200</v>
       </c>
       <c r="J88" t="n">
-        <v>870.4000000000001</v>
+        <v>1638</v>
       </c>
       <c r="K88" t="n">
-        <v>28.35</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="89">
@@ -3070,15 +3194,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2908.8</v>
-      </c>
-      <c r="D89" t="n">
-        <v>2900</v>
-      </c>
+        <v>3636</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>2570</v>
+        <v>3470</v>
       </c>
       <c r="H89" t="n">
         <v>1900</v>
@@ -3087,10 +3209,10 @@
         <v>1900</v>
       </c>
       <c r="J89" t="n">
-        <v>1008.8</v>
+        <v>1736</v>
       </c>
       <c r="K89" t="n">
-        <v>34.68</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="90">
@@ -3101,15 +3223,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2585.6</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2900</v>
-      </c>
+        <v>3232</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>2570</v>
+        <v>3470</v>
       </c>
       <c r="H90" t="n">
         <v>1900</v>
@@ -3118,10 +3238,10 @@
         <v>1900</v>
       </c>
       <c r="J90" t="n">
-        <v>685.6000000000004</v>
+        <v>1332</v>
       </c>
       <c r="K90" t="n">
-        <v>26.52</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="91">
@@ -3132,15 +3252,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2424</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2900</v>
-      </c>
+        <v>3030</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>2470</v>
+        <v>3270</v>
       </c>
       <c r="H91" t="n">
         <v>1600</v>
@@ -3149,10 +3267,10 @@
         <v>1600</v>
       </c>
       <c r="J91" t="n">
-        <v>824</v>
+        <v>1430</v>
       </c>
       <c r="K91" t="n">
-        <v>33.99</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="92">
@@ -3163,15 +3281,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2262.4</v>
-      </c>
-      <c r="D92" t="n">
-        <v>2200</v>
-      </c>
+        <v>2828</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>2470</v>
+        <v>3270</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
@@ -3180,10 +3296,10 @@
         <v>1600</v>
       </c>
       <c r="J92" t="n">
-        <v>662.4000000000001</v>
+        <v>1228</v>
       </c>
       <c r="K92" t="n">
-        <v>29.28</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="93">
@@ -3227,25 +3343,25 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3589.6</v>
+        <v>4487</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>4200</v>
+        <v>5500</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>3670</v>
+        <v>3970</v>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>3589.6</v>
+        <v>3970</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="95">
@@ -3256,25 +3372,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3410.4</v>
+        <v>4263</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>3866.67</v>
+        <v>4100</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>3470</v>
+        <v>3770</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>3410.4</v>
+        <v>3770</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="96">
@@ -3285,25 +3401,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3231.2</v>
+        <v>4039</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>2871.43</v>
+        <v>3800</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>3170</v>
+        <v>3470</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>2871.43</v>
+        <v>3470</v>
       </c>
       <c r="J96" t="n">
-        <v>359.7700000000004</v>
+        <v>569</v>
       </c>
       <c r="K96" t="n">
-        <v>11.13</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="97">
@@ -3314,25 +3430,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2872</v>
+        <v>3590</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>2835.71</v>
+        <v>3300</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>3170</v>
+        <v>3470</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>2835.71</v>
+        <v>3300</v>
       </c>
       <c r="J97" t="n">
-        <v>36.28999999999996</v>
+        <v>290</v>
       </c>
       <c r="K97" t="n">
-        <v>1.26</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="98">
@@ -3343,25 +3459,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2692.8</v>
+        <v>3366</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>2823.81</v>
+        <v>3100</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>2970</v>
+        <v>3270</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>2692.8</v>
+        <v>3100</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="99">
@@ -3372,25 +3488,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2512.8</v>
+        <v>3141</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>2816.67</v>
+        <v>2800</v>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>2970</v>
+        <v>3270</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>2512.8</v>
+        <v>2800</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="100">
@@ -3582,7 +3698,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Renault Kaptur AT Promo</t>
+          <t>Hyundai Creta II AT Promo</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -3602,29 +3718,29 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3760.8</v>
+        <v>4701</v>
       </c>
       <c r="D108" t="n">
         <v>3700</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
-        <v>3770</v>
+        <v>3900</v>
       </c>
       <c r="G108" t="n">
-        <v>3270</v>
+        <v>4170</v>
       </c>
       <c r="H108" t="n">
         <v>3900</v>
       </c>
       <c r="I108" t="n">
-        <v>3270</v>
+        <v>3700</v>
       </c>
       <c r="J108" t="n">
-        <v>490.8000000000002</v>
+        <v>1001</v>
       </c>
       <c r="K108" t="n">
-        <v>13.05</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="109">
@@ -3635,29 +3751,29 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3572.8</v>
+        <v>4466</v>
       </c>
       <c r="D109" t="n">
         <v>3700</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>3250</v>
+        <v>3700</v>
       </c>
       <c r="G109" t="n">
-        <v>3070</v>
+        <v>3870</v>
       </c>
       <c r="H109" t="n">
         <v>3900</v>
       </c>
       <c r="I109" t="n">
-        <v>3070</v>
+        <v>3700</v>
       </c>
       <c r="J109" t="n">
-        <v>502.8000000000002</v>
+        <v>766</v>
       </c>
       <c r="K109" t="n">
-        <v>14.07</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="110">
@@ -3668,29 +3784,29 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3384.8</v>
+        <v>4231</v>
       </c>
       <c r="D110" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>3140</v>
+        <v>3510</v>
       </c>
       <c r="G110" t="n">
-        <v>2870</v>
+        <v>3570</v>
       </c>
       <c r="H110" t="n">
         <v>3500</v>
       </c>
       <c r="I110" t="n">
-        <v>2870</v>
+        <v>3300</v>
       </c>
       <c r="J110" t="n">
-        <v>514.8000000000002</v>
+        <v>931</v>
       </c>
       <c r="K110" t="n">
-        <v>15.21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111">
@@ -3701,29 +3817,29 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3008.8</v>
+        <v>3761</v>
       </c>
       <c r="D111" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
-        <v>3140</v>
+        <v>3510</v>
       </c>
       <c r="G111" t="n">
-        <v>2870</v>
+        <v>3570</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
       </c>
       <c r="I111" t="n">
-        <v>2870</v>
+        <v>3300</v>
       </c>
       <c r="J111" t="n">
-        <v>138.8000000000002</v>
+        <v>461</v>
       </c>
       <c r="K111" t="n">
-        <v>4.61</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="112">
@@ -3734,17 +3850,17 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2632.8</v>
+        <v>3291</v>
       </c>
       <c r="D112" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>3040</v>
+        <v>3323.33</v>
       </c>
       <c r="G112" t="n">
-        <v>2670</v>
+        <v>3370</v>
       </c>
       <c r="H112" t="n">
         <v>2500</v>
@@ -3753,10 +3869,10 @@
         <v>2500</v>
       </c>
       <c r="J112" t="n">
-        <v>132.8000000000002</v>
+        <v>791</v>
       </c>
       <c r="K112" t="n">
-        <v>5.04</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="113">
@@ -3767,17 +3883,17 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2632.8</v>
+        <v>3291</v>
       </c>
       <c r="D113" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>3217.33</v>
+        <v>3361.33</v>
       </c>
       <c r="G113" t="n">
-        <v>2670</v>
+        <v>3370</v>
       </c>
       <c r="H113" t="n">
         <v>2500</v>
@@ -3786,10 +3902,10 @@
         <v>2500</v>
       </c>
       <c r="J113" t="n">
-        <v>132.8000000000002</v>
+        <v>791</v>
       </c>
       <c r="K113" t="n">
-        <v>5.04</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="114">
@@ -3821,7 +3937,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3137.5</v>
+        <v>6275</v>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
@@ -3829,7 +3945,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>3137.5</v>
+        <v>6275</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -3846,7 +3962,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2981</v>
+        <v>5962</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -3854,7 +3970,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>2981</v>
+        <v>5962</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -3871,7 +3987,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2824</v>
+        <v>5648</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -3879,7 +3995,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>2824</v>
+        <v>5648</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -3896,7 +4012,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2510</v>
+        <v>5020</v>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
@@ -3904,7 +4020,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>2510</v>
+        <v>5020</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -3921,7 +4037,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2196.5</v>
+        <v>4393</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -3929,7 +4045,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>2196.5</v>
+        <v>4393</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -3946,7 +4062,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2196.5</v>
+        <v>4393</v>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
@@ -3954,7 +4070,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>2196.5</v>
+        <v>4393</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -3984,11 +4100,7 @@
           <t>Haval Jolion</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Haval Jolion</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t xml:space="preserve">Haval M6 </t>
@@ -3996,7 +4108,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Haval Jolion AT</t>
+          <t>Geely Coolray Promo</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -4016,31 +4128,29 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3137.5</v>
+        <v>6275</v>
       </c>
       <c r="D122" t="n">
-        <v>3700</v>
-      </c>
-      <c r="E122" t="n">
-        <v>4200</v>
-      </c>
+        <v>3800</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G122" t="n">
-        <v>3970</v>
+        <v>4170</v>
       </c>
       <c r="H122" t="n">
         <v>3500</v>
       </c>
       <c r="I122" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="J122" t="n">
-        <v>637.5</v>
+        <v>2775</v>
       </c>
       <c r="K122" t="n">
-        <v>20.32</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="123">
@@ -4051,31 +4161,29 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2981</v>
+        <v>5962</v>
       </c>
       <c r="D123" t="n">
-        <v>3700</v>
-      </c>
-      <c r="E123" t="n">
-        <v>3866.67</v>
-      </c>
+        <v>3800</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>2500</v>
+        <v>3330</v>
       </c>
       <c r="G123" t="n">
-        <v>3770</v>
+        <v>3870</v>
       </c>
       <c r="H123" t="n">
         <v>3500</v>
       </c>
       <c r="I123" t="n">
-        <v>2500</v>
+        <v>3330</v>
       </c>
       <c r="J123" t="n">
-        <v>481</v>
+        <v>2632</v>
       </c>
       <c r="K123" t="n">
-        <v>16.14</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="124">
@@ -4086,31 +4194,29 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2824</v>
+        <v>5648</v>
       </c>
       <c r="D124" t="n">
         <v>3300</v>
       </c>
-      <c r="E124" t="n">
-        <v>2871.43</v>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="G124" t="n">
-        <v>3470</v>
+        <v>3570</v>
       </c>
       <c r="H124" t="n">
         <v>3300</v>
       </c>
       <c r="I124" t="n">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="J124" t="n">
-        <v>324</v>
+        <v>2498</v>
       </c>
       <c r="K124" t="n">
-        <v>11.47</v>
+        <v>44.23</v>
       </c>
     </row>
     <row r="125">
@@ -4121,31 +4227,29 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2510</v>
+        <v>5020</v>
       </c>
       <c r="D125" t="n">
         <v>3300</v>
       </c>
-      <c r="E125" t="n">
-        <v>2835.71</v>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="G125" t="n">
-        <v>3470</v>
+        <v>3570</v>
       </c>
       <c r="H125" t="n">
         <v>3300</v>
       </c>
       <c r="I125" t="n">
-        <v>2500</v>
+        <v>3150</v>
       </c>
       <c r="J125" t="n">
-        <v>10</v>
+        <v>1870</v>
       </c>
       <c r="K125" t="n">
-        <v>0.4</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="126">
@@ -4156,31 +4260,29 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2196.5</v>
+        <v>4393</v>
       </c>
       <c r="D126" t="n">
         <v>3300</v>
       </c>
-      <c r="E126" t="n">
-        <v>2823.81</v>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>2500</v>
+        <v>2980</v>
       </c>
       <c r="G126" t="n">
-        <v>3270</v>
+        <v>3370</v>
       </c>
       <c r="H126" t="n">
         <v>2500</v>
       </c>
       <c r="I126" t="n">
-        <v>2196.5</v>
+        <v>2500</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1893</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="127">
@@ -4191,31 +4293,29 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2196.5</v>
+        <v>4393</v>
       </c>
       <c r="D127" t="n">
         <v>2800</v>
       </c>
-      <c r="E127" t="n">
-        <v>2816.67</v>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>2754.33</v>
+        <v>2980</v>
       </c>
       <c r="G127" t="n">
-        <v>3270</v>
+        <v>3370</v>
       </c>
       <c r="H127" t="n">
         <v>2500</v>
       </c>
       <c r="I127" t="n">
-        <v>2196.5</v>
+        <v>2500</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1893</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="128">
@@ -4251,7 +4351,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>5987.200000000001</v>
+        <v>7484</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -4259,7 +4359,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>5987.200000000001</v>
+        <v>7484</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -4276,7 +4376,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5688</v>
+        <v>7110</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -4284,7 +4384,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>5688</v>
+        <v>7110</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -4301,7 +4401,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5388.8</v>
+        <v>6736</v>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
@@ -4309,7 +4409,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>5388.8</v>
+        <v>6736</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -4326,7 +4426,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4790.400000000001</v>
+        <v>5988</v>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
@@ -4334,7 +4434,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>4790.400000000001</v>
+        <v>5988</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -4351,7 +4451,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4191.2</v>
+        <v>5239</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -4359,7 +4459,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>4191.2</v>
+        <v>5239</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -4376,7 +4476,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4191.2</v>
+        <v>5239</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -4384,7 +4484,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>4191.2</v>
+        <v>5239</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -4426,7 +4526,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nissan X-Trail AT</t>
+          <t>Haval F7 AT</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -4446,31 +4546,31 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>5987.200000000001</v>
+        <v>7484</v>
       </c>
       <c r="D136" t="n">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="E136" t="n">
-        <v>6308</v>
+        <v>9100</v>
       </c>
       <c r="F136" t="n">
-        <v>3470</v>
+        <v>4460</v>
       </c>
       <c r="G136" t="n">
-        <v>4770</v>
+        <v>4970</v>
       </c>
       <c r="H136" t="n">
         <v>3900</v>
       </c>
       <c r="I136" t="n">
-        <v>3470</v>
+        <v>3900</v>
       </c>
       <c r="J136" t="n">
-        <v>2517.200000000001</v>
+        <v>3584</v>
       </c>
       <c r="K136" t="n">
-        <v>42.04</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="137">
@@ -4481,31 +4581,31 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5688</v>
+        <v>7110</v>
       </c>
       <c r="D137" t="n">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="E137" t="n">
-        <v>5974.33</v>
+        <v>8100</v>
       </c>
       <c r="F137" t="n">
-        <v>3470</v>
+        <v>4240</v>
       </c>
       <c r="G137" t="n">
-        <v>4470</v>
+        <v>4670</v>
       </c>
       <c r="H137" t="n">
         <v>3900</v>
       </c>
       <c r="I137" t="n">
-        <v>3470</v>
+        <v>3900</v>
       </c>
       <c r="J137" t="n">
-        <v>2218</v>
+        <v>3210</v>
       </c>
       <c r="K137" t="n">
-        <v>38.99</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="138">
@@ -4516,31 +4616,31 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5388.8</v>
+        <v>6736</v>
       </c>
       <c r="D138" t="n">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="E138" t="n">
-        <v>5304</v>
+        <v>6250</v>
       </c>
       <c r="F138" t="n">
-        <v>3470</v>
+        <v>4020</v>
       </c>
       <c r="G138" t="n">
-        <v>4170</v>
+        <v>4270</v>
       </c>
       <c r="H138" t="n">
         <v>3700</v>
       </c>
       <c r="I138" t="n">
-        <v>3470</v>
+        <v>3700</v>
       </c>
       <c r="J138" t="n">
-        <v>1918.8</v>
+        <v>3036</v>
       </c>
       <c r="K138" t="n">
-        <v>35.61</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="139">
@@ -4551,31 +4651,31 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4790.400000000001</v>
+        <v>5988</v>
       </c>
       <c r="D139" t="n">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="E139" t="n">
-        <v>5268.21</v>
+        <v>5500</v>
       </c>
       <c r="F139" t="n">
-        <v>3470</v>
+        <v>4020</v>
       </c>
       <c r="G139" t="n">
-        <v>4170</v>
+        <v>4270</v>
       </c>
       <c r="H139" t="n">
         <v>3700</v>
       </c>
       <c r="I139" t="n">
-        <v>3470</v>
+        <v>3700</v>
       </c>
       <c r="J139" t="n">
-        <v>1320.400000000001</v>
+        <v>2288</v>
       </c>
       <c r="K139" t="n">
-        <v>27.56</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="140">
@@ -4586,19 +4686,19 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4191.2</v>
+        <v>5239</v>
       </c>
       <c r="D140" t="n">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="E140" t="n">
-        <v>5256.33</v>
+        <v>5300</v>
       </c>
       <c r="F140" t="n">
-        <v>3260</v>
+        <v>3817.62</v>
       </c>
       <c r="G140" t="n">
-        <v>3870</v>
+        <v>3970</v>
       </c>
       <c r="H140" t="n">
         <v>2700</v>
@@ -4607,10 +4707,10 @@
         <v>2700</v>
       </c>
       <c r="J140" t="n">
-        <v>1491.2</v>
+        <v>2539</v>
       </c>
       <c r="K140" t="n">
-        <v>35.58</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="141">
@@ -4621,19 +4721,19 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4191.2</v>
+        <v>5239</v>
       </c>
       <c r="D141" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="E141" t="n">
-        <v>4674.17</v>
+        <v>4800</v>
       </c>
       <c r="F141" t="n">
-        <v>3530.67</v>
+        <v>3896.33</v>
       </c>
       <c r="G141" t="n">
-        <v>3870</v>
+        <v>3970</v>
       </c>
       <c r="H141" t="n">
         <v>2700</v>
@@ -4642,10 +4742,10 @@
         <v>2700</v>
       </c>
       <c r="J141" t="n">
-        <v>1491.2</v>
+        <v>2539</v>
       </c>
       <c r="K141" t="n">
-        <v>35.58</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="142">
@@ -4664,16 +4764,8 @@
           <t>Volkswagen Caravelle T6 Di; Hyundai H-1 II rest. 2</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Hyundai Staria</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Volkswagen Caravelle</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>Hyundai H-1 AT</t>
@@ -4697,23 +4789,19 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5788.5</v>
-      </c>
-      <c r="D143" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E143" t="n">
-        <v>11000</v>
-      </c>
+        <v>6810</v>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>8080</v>
       </c>
       <c r="G143" t="n">
-        <v>8670</v>
+        <v>11270</v>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>5788.5</v>
+        <v>6810</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -4730,23 +4818,19 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>5499.5</v>
-      </c>
-      <c r="D144" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E144" t="n">
-        <v>9833.33</v>
-      </c>
+        <v>6470</v>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>7390</v>
       </c>
       <c r="G144" t="n">
-        <v>8170</v>
+        <v>10570</v>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>5499.5</v>
+        <v>6470</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -4763,23 +4847,19 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>5209.65</v>
-      </c>
-      <c r="D145" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E145" t="n">
-        <v>7971.43</v>
-      </c>
+        <v>6129</v>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>6930</v>
       </c>
       <c r="G145" t="n">
-        <v>7470</v>
+        <v>9670</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
-        <v>5209.65</v>
+        <v>6129</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -4796,23 +4876,19 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4630.8</v>
-      </c>
-      <c r="D146" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E146" t="n">
-        <v>6835.71</v>
-      </c>
+        <v>5448</v>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>6930</v>
       </c>
       <c r="G146" t="n">
-        <v>7470</v>
+        <v>9670</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>4630.8</v>
+        <v>5448</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -4829,23 +4905,19 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4051.95</v>
-      </c>
-      <c r="D147" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E147" t="n">
-        <v>6423.81</v>
-      </c>
+        <v>4767</v>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>6460</v>
       </c>
       <c r="G147" t="n">
-        <v>6970</v>
+        <v>9070</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>4051.95</v>
+        <v>4767</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -4862,23 +4934,19 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>4051.95</v>
-      </c>
-      <c r="D148" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E148" t="n">
-        <v>6016.67</v>
-      </c>
+        <v>4767</v>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>6460</v>
       </c>
       <c r="G148" t="n">
-        <v>6970</v>
+        <v>9070</v>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>4051.95</v>
+        <v>4767</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -4916,7 +4984,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7235.2</v>
+        <v>8512</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
@@ -4924,7 +4992,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>7235.2</v>
+        <v>8512</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -4941,7 +5009,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6873.95</v>
+        <v>8087</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
@@ -4949,7 +5017,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>6873.95</v>
+        <v>8087</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -4966,7 +5034,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6511.849999999999</v>
+        <v>7661</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
@@ -4974,7 +5042,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>6511.849999999999</v>
+        <v>7661</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -4991,7 +5059,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>5788.5</v>
+        <v>6810</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
@@ -4999,7 +5067,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>5788.5</v>
+        <v>6810</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -5016,7 +5084,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>5065.15</v>
+        <v>5959</v>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
@@ -5024,7 +5092,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>5065.15</v>
+        <v>5959</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -5041,7 +5109,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5065.15</v>
+        <v>5959</v>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
@@ -5049,7 +5117,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>5065.15</v>
+        <v>5959</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>

--- a/outputs/analysiss.xlsx
+++ b/outputs/analysiss.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="not in the list cars" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08-05-2024_@_17_56" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-09-2024_@_14_43" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Solaris SH</t>
+          <t>Solaris New 2024</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geely Belgee X50</t>
+          <t>Сhangan Alsvin</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haval Jolion 2WD</t>
+          <t>Solaris HS</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Haval Jolion 4WD</t>
+          <t>Geely Belgee X50</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Changan UNI-K</t>
+          <t>Haval Jolion 2WD</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Geely Emgrand</t>
+          <t>Haval Jolion 4WD</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gac GS8 II</t>
+          <t>Haval F7X</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Geely Atlas NEW Promo</t>
+          <t>Chery Tiggo 7 Pro Max</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Geely Emgrand</t>
+          <t>Changan UNI-K</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Belgee X50</t>
+          <t>GAC M8</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hyundai Tucson IV AT</t>
+          <t>Geely Emgrand</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Geely Atlas NEW</t>
+          <t xml:space="preserve">Belgee X50 </t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Voyah Free</t>
+          <t>Gac GS3</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zeekr 001</t>
+          <t xml:space="preserve">Geely Preface </t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zeekr 009</t>
+          <t>Geely Preface Flagship</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Changan  UNI-K</t>
+          <t>Geely Atlas New 4 WD</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Changan CS 55 PLUS</t>
+          <t>Gac GS8 II</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Changan UNI-T</t>
+          <t>Zeekr 009</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Changan EADO</t>
+          <t>Changan  UNI-K</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jaguar XE ВК49865</t>
+          <t>Changan CS 55 PLUS</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zeekr 001</t>
+          <t>Changan UNI-T</t>
         </is>
       </c>
     </row>
@@ -687,6 +687,36 @@
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>Changan EADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jaguar XE ВК49865</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Zeekr 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Lixang Li 9</t>
         </is>
@@ -703,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,40 +754,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RENT-MOTORS-08-05-24</t>
+          <t>RENT-MOTORS-06-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>REX-RENT-08-05-24</t>
+          <t>REX-RENT-06-09-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>A-ARENDA-08-05-24</t>
+          <t>A-ARENDA-06-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ALMAK-08-05-24</t>
+          <t>STORLET-06-09-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>STORLET-08-05-24</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DELTA</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>DELTA</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>DELTA %</t>
         </is>
@@ -786,7 +811,6 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
@@ -802,14 +826,13 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2634</v>
+      </c>
       <c r="I3" t="n">
-        <v>2634</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -827,14 +850,13 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>2503</v>
+      </c>
       <c r="I4" t="n">
-        <v>2503</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -852,14 +874,13 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>2371</v>
+      </c>
       <c r="I5" t="n">
-        <v>2371</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -877,14 +898,13 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>2187</v>
+      </c>
       <c r="I6" t="n">
-        <v>2187</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -902,14 +922,13 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>2055</v>
+      </c>
       <c r="I7" t="n">
-        <v>2055</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -927,14 +946,13 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>1976</v>
+      </c>
       <c r="I8" t="n">
-        <v>1976</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,7 +975,6 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -973,14 +990,13 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>3292</v>
+      </c>
       <c r="I10" t="n">
-        <v>3292</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -998,14 +1014,13 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>3128</v>
+      </c>
       <c r="I11" t="n">
-        <v>3128</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1023,14 +1038,13 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>2963</v>
+      </c>
       <c r="I12" t="n">
-        <v>2963</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1048,14 +1062,13 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>2733</v>
+      </c>
       <c r="I13" t="n">
-        <v>2733</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1073,14 +1086,13 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>2568</v>
+      </c>
       <c r="I14" t="n">
-        <v>2568</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1098,14 +1110,13 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>2469</v>
+      </c>
       <c r="I15" t="n">
-        <v>2469</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,7 +1139,6 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -1144,14 +1154,13 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -1167,14 +1176,13 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -1190,14 +1198,13 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -1213,14 +1220,13 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -1236,14 +1242,13 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
@@ -1259,14 +1264,13 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1287,15 +1291,10 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Lada Largus 7 мест MT</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -1310,18 +1309,15 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>3770</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>3859</v>
+      </c>
       <c r="I24" t="n">
-        <v>3770</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>89</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1337,18 +1333,15 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>3570</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>3667</v>
+      </c>
       <c r="I25" t="n">
-        <v>3570</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>97</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1364,18 +1357,15 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>3270</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>3474</v>
+      </c>
       <c r="I26" t="n">
-        <v>3270</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>204</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1391,17 +1381,14 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
-        <v>3270</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>3088</v>
+      </c>
       <c r="I27" t="n">
-        <v>3088</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1418,17 +1405,14 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
-        <v>3070</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>2702</v>
+      </c>
       <c r="I28" t="n">
-        <v>2702</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1445,17 +1429,14 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="n">
-        <v>3070</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>2702</v>
+      </c>
       <c r="I29" t="n">
-        <v>2702</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1482,7 +1463,6 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1498,14 +1478,13 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>2861</v>
+      </c>
       <c r="I31" t="n">
-        <v>2861</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1523,14 +1502,13 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>2718</v>
+      </c>
       <c r="I32" t="n">
-        <v>2718</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1548,14 +1526,13 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>2575</v>
+      </c>
       <c r="I33" t="n">
-        <v>2575</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1573,14 +1550,13 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>2375</v>
+      </c>
       <c r="I34" t="n">
-        <v>2375</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1598,14 +1574,13 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>2232</v>
+      </c>
       <c r="I35" t="n">
-        <v>2232</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1623,14 +1598,13 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>2146</v>
+      </c>
       <c r="I36" t="n">
-        <v>2146</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1655,11 +1629,7 @@
           <t>Hyundai Solaris</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Сhangan Alsvin / Renault Logan</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>Hyundai  Solaris 1.6  AT</t>
@@ -1667,17 +1637,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hyundai Solaris II Promo</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
           <t>Hyundai Solaris sedan</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
@@ -1690,27 +1655,22 @@
         <v>3576</v>
       </c>
       <c r="D38" t="n">
-        <v>2600</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3800</v>
-      </c>
+        <v>3120</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>3330</v>
+        <v>3430</v>
       </c>
       <c r="G38" t="n">
-        <v>2770</v>
+        <v>2000</v>
       </c>
       <c r="H38" t="n">
         <v>2000</v>
       </c>
       <c r="I38" t="n">
-        <v>2000</v>
+        <v>1576</v>
       </c>
       <c r="J38" t="n">
-        <v>1576</v>
-      </c>
-      <c r="K38" t="n">
         <v>44.07</v>
       </c>
     </row>
@@ -1725,27 +1685,22 @@
         <v>3398</v>
       </c>
       <c r="D39" t="n">
-        <v>2600</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3100</v>
-      </c>
+        <v>3120</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>2990</v>
+        <v>3090</v>
       </c>
       <c r="G39" t="n">
-        <v>2570</v>
+        <v>2000</v>
       </c>
       <c r="H39" t="n">
         <v>2000</v>
       </c>
       <c r="I39" t="n">
-        <v>2000</v>
+        <v>1398</v>
       </c>
       <c r="J39" t="n">
-        <v>1398</v>
-      </c>
-      <c r="K39" t="n">
         <v>41.14</v>
       </c>
     </row>
@@ -1760,27 +1715,22 @@
         <v>3219</v>
       </c>
       <c r="D40" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2900</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>2860</v>
+        <v>2950</v>
       </c>
       <c r="G40" t="n">
-        <v>2470</v>
+        <v>1800</v>
       </c>
       <c r="H40" t="n">
         <v>1800</v>
       </c>
       <c r="I40" t="n">
-        <v>1800</v>
+        <v>1419</v>
       </c>
       <c r="J40" t="n">
-        <v>1419</v>
-      </c>
-      <c r="K40" t="n">
         <v>44.08</v>
       </c>
     </row>
@@ -1795,27 +1745,22 @@
         <v>2969</v>
       </c>
       <c r="D41" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2600</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>2860</v>
+        <v>2950</v>
       </c>
       <c r="G41" t="n">
-        <v>2470</v>
+        <v>1800</v>
       </c>
       <c r="H41" t="n">
         <v>1800</v>
       </c>
       <c r="I41" t="n">
-        <v>1800</v>
+        <v>1169</v>
       </c>
       <c r="J41" t="n">
-        <v>1169</v>
-      </c>
-      <c r="K41" t="n">
         <v>39.37</v>
       </c>
     </row>
@@ -1830,27 +1775,22 @@
         <v>2790</v>
       </c>
       <c r="D42" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2500</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>2660</v>
+        <v>2740</v>
       </c>
       <c r="G42" t="n">
-        <v>2270</v>
+        <v>1500</v>
       </c>
       <c r="H42" t="n">
         <v>1500</v>
       </c>
       <c r="I42" t="n">
-        <v>1500</v>
+        <v>1290</v>
       </c>
       <c r="J42" t="n">
-        <v>1290</v>
-      </c>
-      <c r="K42" t="n">
         <v>46.24</v>
       </c>
     </row>
@@ -1865,27 +1805,22 @@
         <v>2682</v>
       </c>
       <c r="D43" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2420</v>
-      </c>
+        <v>2640</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>2660</v>
+        <v>2740</v>
       </c>
       <c r="G43" t="n">
-        <v>2270</v>
+        <v>1500</v>
       </c>
       <c r="H43" t="n">
         <v>1500</v>
       </c>
       <c r="I43" t="n">
-        <v>1500</v>
+        <v>1182</v>
       </c>
       <c r="J43" t="n">
-        <v>1182</v>
-      </c>
-      <c r="K43" t="n">
         <v>44.07</v>
       </c>
     </row>
@@ -1912,7 +1847,6 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
@@ -1928,14 +1862,13 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>3305</v>
+      </c>
       <c r="I45" t="n">
-        <v>3305</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1953,14 +1886,13 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>3140</v>
+      </c>
       <c r="I46" t="n">
-        <v>3140</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1978,14 +1910,13 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>2975</v>
+      </c>
       <c r="I47" t="n">
-        <v>2975</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2003,14 +1934,13 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>2644</v>
+      </c>
       <c r="I48" t="n">
-        <v>2644</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2028,14 +1958,13 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>2314</v>
+      </c>
       <c r="I49" t="n">
-        <v>2314</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2053,14 +1982,13 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>2314</v>
+      </c>
       <c r="I50" t="n">
-        <v>2314</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2085,17 +2013,12 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Volkswagen Polo АТ Promo</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
           <t xml:space="preserve">Skoda Rapid </t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
@@ -2111,18 +2034,15 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>2770</v>
+        <v>1800</v>
       </c>
       <c r="H52" t="n">
         <v>1800</v>
       </c>
       <c r="I52" t="n">
-        <v>1800</v>
+        <v>2331</v>
       </c>
       <c r="J52" t="n">
-        <v>2331</v>
-      </c>
-      <c r="K52" t="n">
         <v>56.43</v>
       </c>
     </row>
@@ -2140,18 +2060,15 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>2570</v>
+        <v>1800</v>
       </c>
       <c r="H53" t="n">
         <v>1800</v>
       </c>
       <c r="I53" t="n">
-        <v>1800</v>
+        <v>2125</v>
       </c>
       <c r="J53" t="n">
-        <v>2125</v>
-      </c>
-      <c r="K53" t="n">
         <v>54.14</v>
       </c>
     </row>
@@ -2169,18 +2086,15 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>2470</v>
+        <v>1600</v>
       </c>
       <c r="H54" t="n">
         <v>1600</v>
       </c>
       <c r="I54" t="n">
-        <v>1600</v>
+        <v>2118</v>
       </c>
       <c r="J54" t="n">
-        <v>2118</v>
-      </c>
-      <c r="K54" t="n">
         <v>56.97</v>
       </c>
     </row>
@@ -2198,18 +2112,15 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>2470</v>
+        <v>1600</v>
       </c>
       <c r="H55" t="n">
         <v>1600</v>
       </c>
       <c r="I55" t="n">
-        <v>1600</v>
+        <v>1705</v>
       </c>
       <c r="J55" t="n">
-        <v>1705</v>
-      </c>
-      <c r="K55" t="n">
         <v>51.59</v>
       </c>
     </row>
@@ -2227,18 +2138,15 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>2270</v>
+        <v>1400</v>
       </c>
       <c r="H56" t="n">
         <v>1400</v>
       </c>
       <c r="I56" t="n">
-        <v>1400</v>
+        <v>1492</v>
       </c>
       <c r="J56" t="n">
-        <v>1492</v>
-      </c>
-      <c r="K56" t="n">
         <v>51.59</v>
       </c>
     </row>
@@ -2256,18 +2164,15 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>2270</v>
+        <v>1400</v>
       </c>
       <c r="H57" t="n">
         <v>1400</v>
       </c>
       <c r="I57" t="n">
-        <v>1400</v>
+        <v>1492</v>
       </c>
       <c r="J57" t="n">
-        <v>1492</v>
-      </c>
-      <c r="K57" t="n">
         <v>51.59</v>
       </c>
     </row>
@@ -2294,15 +2199,14 @@
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Skoda Octavia</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
@@ -2315,22 +2219,21 @@
         <v>3690</v>
       </c>
       <c r="D59" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>3200</v>
+      </c>
       <c r="H59" t="n">
         <v>3200</v>
       </c>
       <c r="I59" t="n">
-        <v>3000</v>
+        <v>490</v>
       </c>
       <c r="J59" t="n">
-        <v>690</v>
-      </c>
-      <c r="K59" t="n">
-        <v>18.7</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="60">
@@ -2344,22 +2247,21 @@
         <v>3506</v>
       </c>
       <c r="D60" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>3200</v>
+      </c>
       <c r="H60" t="n">
         <v>3200</v>
       </c>
       <c r="I60" t="n">
-        <v>3000</v>
+        <v>306</v>
       </c>
       <c r="J60" t="n">
-        <v>506</v>
-      </c>
-      <c r="K60" t="n">
-        <v>14.43</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="61">
@@ -2373,22 +2275,21 @@
         <v>3321</v>
       </c>
       <c r="D61" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>2900</v>
+      </c>
       <c r="H61" t="n">
         <v>2900</v>
       </c>
       <c r="I61" t="n">
-        <v>2600</v>
+        <v>421</v>
       </c>
       <c r="J61" t="n">
-        <v>721</v>
-      </c>
-      <c r="K61" t="n">
-        <v>21.71</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="62">
@@ -2402,22 +2303,21 @@
         <v>2952</v>
       </c>
       <c r="D62" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>2900</v>
+      </c>
       <c r="H62" t="n">
         <v>2900</v>
       </c>
       <c r="I62" t="n">
-        <v>2600</v>
+        <v>52</v>
       </c>
       <c r="J62" t="n">
-        <v>352</v>
-      </c>
-      <c r="K62" t="n">
-        <v>11.92</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="63">
@@ -2431,21 +2331,20 @@
         <v>2583</v>
       </c>
       <c r="D63" t="n">
-        <v>2600</v>
+        <v>3120</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>2500</v>
+      </c>
       <c r="H63" t="n">
         <v>2500</v>
       </c>
       <c r="I63" t="n">
-        <v>2500</v>
+        <v>83</v>
       </c>
       <c r="J63" t="n">
-        <v>83</v>
-      </c>
-      <c r="K63" t="n">
         <v>3.21</v>
       </c>
     </row>
@@ -2460,22 +2359,21 @@
         <v>2583</v>
       </c>
       <c r="D64" t="n">
-        <v>2400</v>
+        <v>2880</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>2500</v>
+      </c>
       <c r="H64" t="n">
         <v>2500</v>
       </c>
       <c r="I64" t="n">
-        <v>2400</v>
+        <v>83</v>
       </c>
       <c r="J64" t="n">
-        <v>183</v>
-      </c>
-      <c r="K64" t="n">
-        <v>7.08</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="65">
@@ -2495,17 +2393,20 @@
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Changan UNI-V</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Kia Ceed</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n"/>
@@ -2518,19 +2419,20 @@
         <v>4341</v>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>8273</v>
+      </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>2200</v>
+      </c>
       <c r="H66" t="n">
         <v>2200</v>
       </c>
       <c r="I66" t="n">
-        <v>2200</v>
+        <v>2141</v>
       </c>
       <c r="J66" t="n">
-        <v>2141</v>
-      </c>
-      <c r="K66" t="n">
         <v>49.32</v>
       </c>
     </row>
@@ -2545,19 +2447,20 @@
         <v>4124</v>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>6702</v>
+      </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>2200</v>
+      </c>
       <c r="H67" t="n">
         <v>2200</v>
       </c>
       <c r="I67" t="n">
-        <v>2200</v>
+        <v>1924</v>
       </c>
       <c r="J67" t="n">
-        <v>1924</v>
-      </c>
-      <c r="K67" t="n">
         <v>46.65</v>
       </c>
     </row>
@@ -2572,19 +2475,20 @@
         <v>3907</v>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>5969</v>
+      </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>2100</v>
+      </c>
       <c r="H68" t="n">
         <v>2100</v>
       </c>
       <c r="I68" t="n">
-        <v>2100</v>
+        <v>1807</v>
       </c>
       <c r="J68" t="n">
-        <v>1807</v>
-      </c>
-      <c r="K68" t="n">
         <v>46.25</v>
       </c>
     </row>
@@ -2599,19 +2503,20 @@
         <v>3473</v>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>5026.57</v>
+      </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>2100</v>
+      </c>
       <c r="H69" t="n">
         <v>2100</v>
       </c>
       <c r="I69" t="n">
-        <v>2100</v>
+        <v>1373</v>
       </c>
       <c r="J69" t="n">
-        <v>1373</v>
-      </c>
-      <c r="K69" t="n">
         <v>39.53</v>
       </c>
     </row>
@@ -2626,19 +2531,20 @@
         <v>3039</v>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>4817.14</v>
+      </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>2000</v>
+      </c>
       <c r="H70" t="n">
         <v>2000</v>
       </c>
       <c r="I70" t="n">
-        <v>2000</v>
+        <v>1039</v>
       </c>
       <c r="J70" t="n">
-        <v>1039</v>
-      </c>
-      <c r="K70" t="n">
         <v>34.19</v>
       </c>
     </row>
@@ -2653,19 +2559,20 @@
         <v>3039</v>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>4293.53</v>
+      </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>2000</v>
+      </c>
       <c r="H71" t="n">
         <v>2000</v>
       </c>
       <c r="I71" t="n">
-        <v>2000</v>
+        <v>1039</v>
       </c>
       <c r="J71" t="n">
-        <v>1039</v>
-      </c>
-      <c r="K71" t="n">
         <v>34.19</v>
       </c>
     </row>
@@ -2697,22 +2604,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hyundai Sonata VIII 2.5</t>
+          <t>Kia K5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hyundai Sonata AT Promo</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
           <t>Hyundai i40</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n"/>
@@ -2725,27 +2627,24 @@
         <v>5001</v>
       </c>
       <c r="D73" t="n">
-        <v>4300</v>
+        <v>5160</v>
       </c>
       <c r="E73" t="n">
-        <v>9100</v>
+        <v>9530</v>
       </c>
       <c r="F73" t="n">
-        <v>3900</v>
+        <v>5000</v>
       </c>
       <c r="G73" t="n">
-        <v>4370</v>
+        <v>2500</v>
       </c>
       <c r="H73" t="n">
         <v>2500</v>
       </c>
       <c r="I73" t="n">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="J73" t="n">
-        <v>2501</v>
-      </c>
-      <c r="K73" t="n">
         <v>50.01</v>
       </c>
     </row>
@@ -2760,27 +2659,24 @@
         <v>4751</v>
       </c>
       <c r="D74" t="n">
-        <v>4300</v>
+        <v>5160</v>
       </c>
       <c r="E74" t="n">
-        <v>8100</v>
+        <v>8482.33</v>
       </c>
       <c r="F74" t="n">
-        <v>3710</v>
+        <v>4750</v>
       </c>
       <c r="G74" t="n">
-        <v>4070</v>
+        <v>2500</v>
       </c>
       <c r="H74" t="n">
         <v>2500</v>
       </c>
       <c r="I74" t="n">
-        <v>2500</v>
+        <v>2251</v>
       </c>
       <c r="J74" t="n">
-        <v>2251</v>
-      </c>
-      <c r="K74" t="n">
         <v>47.38</v>
       </c>
     </row>
@@ -2795,27 +2691,24 @@
         <v>4501</v>
       </c>
       <c r="D75" t="n">
-        <v>3700</v>
+        <v>4440</v>
       </c>
       <c r="E75" t="n">
-        <v>6250</v>
+        <v>6545</v>
       </c>
       <c r="F75" t="n">
-        <v>3510</v>
+        <v>4500</v>
       </c>
       <c r="G75" t="n">
-        <v>3670</v>
+        <v>2400</v>
       </c>
       <c r="H75" t="n">
         <v>2400</v>
       </c>
       <c r="I75" t="n">
-        <v>2400</v>
+        <v>2101</v>
       </c>
       <c r="J75" t="n">
-        <v>2101</v>
-      </c>
-      <c r="K75" t="n">
         <v>46.68</v>
       </c>
     </row>
@@ -2830,27 +2723,24 @@
         <v>4001</v>
       </c>
       <c r="D76" t="n">
-        <v>3700</v>
+        <v>4440</v>
       </c>
       <c r="E76" t="n">
-        <v>5500</v>
+        <v>5759.57</v>
       </c>
       <c r="F76" t="n">
-        <v>3510</v>
+        <v>4500</v>
       </c>
       <c r="G76" t="n">
-        <v>3670</v>
+        <v>2400</v>
       </c>
       <c r="H76" t="n">
         <v>2400</v>
       </c>
       <c r="I76" t="n">
-        <v>2400</v>
+        <v>1601</v>
       </c>
       <c r="J76" t="n">
-        <v>1601</v>
-      </c>
-      <c r="K76" t="n">
         <v>40.01</v>
       </c>
     </row>
@@ -2865,27 +2755,24 @@
         <v>3501</v>
       </c>
       <c r="D77" t="n">
-        <v>3700</v>
+        <v>4440</v>
       </c>
       <c r="E77" t="n">
-        <v>5300</v>
+        <v>5550.14</v>
       </c>
       <c r="F77" t="n">
-        <v>3347.62</v>
+        <v>4250</v>
       </c>
       <c r="G77" t="n">
-        <v>3570</v>
+        <v>1900</v>
       </c>
       <c r="H77" t="n">
         <v>1900</v>
       </c>
       <c r="I77" t="n">
-        <v>1900</v>
+        <v>1601</v>
       </c>
       <c r="J77" t="n">
-        <v>1601</v>
-      </c>
-      <c r="K77" t="n">
         <v>45.73</v>
       </c>
     </row>
@@ -2900,27 +2787,24 @@
         <v>3501</v>
       </c>
       <c r="D78" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="E78" t="n">
-        <v>4800</v>
+        <v>5026.57</v>
       </c>
       <c r="F78" t="n">
-        <v>3426.33</v>
+        <v>4250</v>
       </c>
       <c r="G78" t="n">
-        <v>3570</v>
+        <v>1900</v>
       </c>
       <c r="H78" t="n">
         <v>1900</v>
       </c>
       <c r="I78" t="n">
-        <v>1900</v>
+        <v>1601</v>
       </c>
       <c r="J78" t="n">
-        <v>1601</v>
-      </c>
-      <c r="K78" t="n">
         <v>45.73</v>
       </c>
     </row>
@@ -2943,7 +2827,6 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n"/>
@@ -2959,14 +2842,13 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>5556</v>
+      </c>
       <c r="I80" t="n">
-        <v>5556</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2984,14 +2866,13 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>5279</v>
+      </c>
       <c r="I81" t="n">
-        <v>5279</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3009,14 +2890,13 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>5001</v>
+      </c>
       <c r="I82" t="n">
-        <v>5001</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3034,14 +2914,13 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>4445</v>
+      </c>
       <c r="I83" t="n">
-        <v>4445</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3059,14 +2938,13 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>3890</v>
+      </c>
       <c r="I84" t="n">
-        <v>3890</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3084,14 +2962,13 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>3890</v>
+      </c>
       <c r="I85" t="n">
-        <v>3890</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3116,17 +2993,12 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hyundai Creta AT</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
           <t>Renault Kaptur</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n"/>
@@ -3142,18 +3014,15 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>3970</v>
+        <v>2200</v>
       </c>
       <c r="H87" t="n">
         <v>2200</v>
       </c>
       <c r="I87" t="n">
-        <v>2200</v>
+        <v>1839</v>
       </c>
       <c r="J87" t="n">
-        <v>1839</v>
-      </c>
-      <c r="K87" t="n">
         <v>45.53</v>
       </c>
     </row>
@@ -3171,18 +3040,15 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>3770</v>
+        <v>2200</v>
       </c>
       <c r="H88" t="n">
         <v>2200</v>
       </c>
       <c r="I88" t="n">
-        <v>2200</v>
+        <v>1638</v>
       </c>
       <c r="J88" t="n">
-        <v>1638</v>
-      </c>
-      <c r="K88" t="n">
         <v>42.68</v>
       </c>
     </row>
@@ -3200,18 +3066,15 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>3470</v>
+        <v>1900</v>
       </c>
       <c r="H89" t="n">
         <v>1900</v>
       </c>
       <c r="I89" t="n">
-        <v>1900</v>
+        <v>1736</v>
       </c>
       <c r="J89" t="n">
-        <v>1736</v>
-      </c>
-      <c r="K89" t="n">
         <v>47.74</v>
       </c>
     </row>
@@ -3229,18 +3092,15 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>3470</v>
+        <v>1900</v>
       </c>
       <c r="H90" t="n">
         <v>1900</v>
       </c>
       <c r="I90" t="n">
-        <v>1900</v>
+        <v>1332</v>
       </c>
       <c r="J90" t="n">
-        <v>1332</v>
-      </c>
-      <c r="K90" t="n">
         <v>41.21</v>
       </c>
     </row>
@@ -3258,18 +3118,15 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>3270</v>
+        <v>1600</v>
       </c>
       <c r="H91" t="n">
         <v>1600</v>
       </c>
       <c r="I91" t="n">
-        <v>1600</v>
+        <v>1430</v>
       </c>
       <c r="J91" t="n">
-        <v>1430</v>
-      </c>
-      <c r="K91" t="n">
         <v>47.19</v>
       </c>
     </row>
@@ -3287,18 +3144,15 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>3270</v>
+        <v>1600</v>
       </c>
       <c r="H92" t="n">
         <v>1600</v>
       </c>
       <c r="I92" t="n">
-        <v>1600</v>
+        <v>1228</v>
       </c>
       <c r="J92" t="n">
-        <v>1228</v>
-      </c>
-      <c r="K92" t="n">
         <v>43.42</v>
       </c>
     </row>
@@ -3319,21 +3173,12 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Сhery Tiggo 4</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Renault Duster 4WD AT</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n"/>
@@ -3346,22 +3191,17 @@
         <v>4487</v>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="n">
-        <v>5500</v>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="n">
-        <v>3970</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="n">
+        <v>4487</v>
+      </c>
       <c r="I94" t="n">
-        <v>3970</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>517</v>
-      </c>
-      <c r="K94" t="n">
-        <v>11.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3375,22 +3215,17 @@
         <v>4263</v>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="n">
-        <v>4100</v>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="n">
-        <v>3770</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>4263</v>
+      </c>
       <c r="I95" t="n">
-        <v>3770</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>493</v>
-      </c>
-      <c r="K95" t="n">
-        <v>11.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3404,22 +3239,17 @@
         <v>4039</v>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="n">
-        <v>3800</v>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="n">
-        <v>3470</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>4039</v>
+      </c>
       <c r="I96" t="n">
-        <v>3470</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>569</v>
-      </c>
-      <c r="K96" t="n">
-        <v>14.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -3433,22 +3263,17 @@
         <v>3590</v>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="n">
-        <v>3300</v>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="n">
-        <v>3470</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>3590</v>
+      </c>
       <c r="I97" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>290</v>
-      </c>
-      <c r="K97" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3462,22 +3287,17 @@
         <v>3366</v>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="n">
-        <v>3100</v>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="n">
-        <v>3270</v>
-      </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>3366</v>
+      </c>
       <c r="I98" t="n">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>266</v>
-      </c>
-      <c r="K98" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3491,22 +3311,17 @@
         <v>3141</v>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="n">
-        <v>2800</v>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="n">
-        <v>3270</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>3141</v>
+      </c>
       <c r="I99" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>341</v>
-      </c>
-      <c r="K99" t="n">
-        <v>10.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3528,7 +3343,6 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n"/>
@@ -3544,14 +3358,13 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n"/>
@@ -3567,14 +3380,13 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n"/>
@@ -3590,14 +3402,13 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n"/>
@@ -3613,14 +3424,13 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n"/>
@@ -3636,14 +3446,13 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n"/>
@@ -3659,14 +3468,13 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -3698,17 +3506,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hyundai Creta II AT Promo</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
           <t>Toyota CH R</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n"/>
@@ -3721,26 +3524,23 @@
         <v>4701</v>
       </c>
       <c r="D108" t="n">
-        <v>3700</v>
+        <v>4440</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
         <v>3900</v>
       </c>
       <c r="G108" t="n">
-        <v>4170</v>
+        <v>3900</v>
       </c>
       <c r="H108" t="n">
         <v>3900</v>
       </c>
       <c r="I108" t="n">
-        <v>3700</v>
+        <v>801</v>
       </c>
       <c r="J108" t="n">
-        <v>1001</v>
-      </c>
-      <c r="K108" t="n">
-        <v>21.29</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="109">
@@ -3754,25 +3554,22 @@
         <v>4466</v>
       </c>
       <c r="D109" t="n">
-        <v>3700</v>
+        <v>4440</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
         <v>3700</v>
       </c>
       <c r="G109" t="n">
-        <v>3870</v>
+        <v>3900</v>
       </c>
       <c r="H109" t="n">
-        <v>3900</v>
+        <v>3700</v>
       </c>
       <c r="I109" t="n">
-        <v>3700</v>
+        <v>766</v>
       </c>
       <c r="J109" t="n">
-        <v>766</v>
-      </c>
-      <c r="K109" t="n">
         <v>17.15</v>
       </c>
     </row>
@@ -3787,26 +3584,23 @@
         <v>4231</v>
       </c>
       <c r="D110" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
         <v>3510</v>
       </c>
       <c r="G110" t="n">
-        <v>3570</v>
+        <v>3500</v>
       </c>
       <c r="H110" t="n">
         <v>3500</v>
       </c>
       <c r="I110" t="n">
-        <v>3300</v>
+        <v>731</v>
       </c>
       <c r="J110" t="n">
-        <v>931</v>
-      </c>
-      <c r="K110" t="n">
-        <v>22</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="111">
@@ -3820,26 +3614,23 @@
         <v>3761</v>
       </c>
       <c r="D111" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
         <v>3510</v>
       </c>
       <c r="G111" t="n">
-        <v>3570</v>
+        <v>3500</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
       </c>
       <c r="I111" t="n">
-        <v>3300</v>
+        <v>261</v>
       </c>
       <c r="J111" t="n">
-        <v>461</v>
-      </c>
-      <c r="K111" t="n">
-        <v>12.26</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="112">
@@ -3853,25 +3644,22 @@
         <v>3291</v>
       </c>
       <c r="D112" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>3323.33</v>
+        <v>3310</v>
       </c>
       <c r="G112" t="n">
-        <v>3370</v>
+        <v>2500</v>
       </c>
       <c r="H112" t="n">
         <v>2500</v>
       </c>
       <c r="I112" t="n">
-        <v>2500</v>
+        <v>791</v>
       </c>
       <c r="J112" t="n">
-        <v>791</v>
-      </c>
-      <c r="K112" t="n">
         <v>24.04</v>
       </c>
     </row>
@@ -3886,25 +3674,22 @@
         <v>3291</v>
       </c>
       <c r="D113" t="n">
-        <v>2800</v>
+        <v>3360</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>3361.33</v>
+        <v>3310</v>
       </c>
       <c r="G113" t="n">
-        <v>3370</v>
+        <v>2500</v>
       </c>
       <c r="H113" t="n">
         <v>2500</v>
       </c>
       <c r="I113" t="n">
-        <v>2500</v>
+        <v>791</v>
       </c>
       <c r="J113" t="n">
-        <v>791</v>
-      </c>
-      <c r="K113" t="n">
         <v>24.04</v>
       </c>
     </row>
@@ -3927,7 +3712,6 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n"/>
@@ -3943,14 +3727,13 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>6275</v>
+      </c>
       <c r="I115" t="n">
-        <v>6275</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3968,14 +3751,13 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>5962</v>
+      </c>
       <c r="I116" t="n">
-        <v>5962</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3993,14 +3775,13 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="n">
+        <v>5648</v>
+      </c>
       <c r="I117" t="n">
-        <v>5648</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4018,14 +3799,13 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>5020</v>
+      </c>
       <c r="I118" t="n">
-        <v>5020</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4043,14 +3823,13 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>4393</v>
+      </c>
       <c r="I119" t="n">
-        <v>4393</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4068,14 +3847,13 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>4393</v>
+      </c>
       <c r="I120" t="n">
-        <v>4393</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4108,17 +3886,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Geely Coolray Promo</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
           <t>Kia Sportage SLS</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n"/>
@@ -4131,25 +3904,22 @@
         <v>6275</v>
       </c>
       <c r="D122" t="n">
-        <v>3800</v>
+        <v>4560</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
         <v>3500</v>
       </c>
       <c r="G122" t="n">
-        <v>4170</v>
+        <v>3500</v>
       </c>
       <c r="H122" t="n">
         <v>3500</v>
       </c>
       <c r="I122" t="n">
-        <v>3500</v>
+        <v>2775</v>
       </c>
       <c r="J122" t="n">
-        <v>2775</v>
-      </c>
-      <c r="K122" t="n">
         <v>44.22</v>
       </c>
     </row>
@@ -4164,25 +3934,22 @@
         <v>5962</v>
       </c>
       <c r="D123" t="n">
-        <v>3800</v>
+        <v>4560</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>3330</v>
       </c>
       <c r="G123" t="n">
-        <v>3870</v>
+        <v>3500</v>
       </c>
       <c r="H123" t="n">
-        <v>3500</v>
+        <v>3330</v>
       </c>
       <c r="I123" t="n">
-        <v>3330</v>
+        <v>2632</v>
       </c>
       <c r="J123" t="n">
-        <v>2632</v>
-      </c>
-      <c r="K123" t="n">
         <v>44.15</v>
       </c>
     </row>
@@ -4197,25 +3964,22 @@
         <v>5648</v>
       </c>
       <c r="D124" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>3150</v>
       </c>
       <c r="G124" t="n">
-        <v>3570</v>
+        <v>3300</v>
       </c>
       <c r="H124" t="n">
-        <v>3300</v>
+        <v>3150</v>
       </c>
       <c r="I124" t="n">
-        <v>3150</v>
+        <v>2498</v>
       </c>
       <c r="J124" t="n">
-        <v>2498</v>
-      </c>
-      <c r="K124" t="n">
         <v>44.23</v>
       </c>
     </row>
@@ -4230,25 +3994,22 @@
         <v>5020</v>
       </c>
       <c r="D125" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>3150</v>
       </c>
       <c r="G125" t="n">
-        <v>3570</v>
+        <v>3300</v>
       </c>
       <c r="H125" t="n">
-        <v>3300</v>
+        <v>3150</v>
       </c>
       <c r="I125" t="n">
-        <v>3150</v>
+        <v>1870</v>
       </c>
       <c r="J125" t="n">
-        <v>1870</v>
-      </c>
-      <c r="K125" t="n">
         <v>37.25</v>
       </c>
     </row>
@@ -4263,25 +4024,22 @@
         <v>4393</v>
       </c>
       <c r="D126" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>2980</v>
       </c>
       <c r="G126" t="n">
-        <v>3370</v>
+        <v>2500</v>
       </c>
       <c r="H126" t="n">
         <v>2500</v>
       </c>
       <c r="I126" t="n">
-        <v>2500</v>
+        <v>1893</v>
       </c>
       <c r="J126" t="n">
-        <v>1893</v>
-      </c>
-      <c r="K126" t="n">
         <v>43.09</v>
       </c>
     </row>
@@ -4296,25 +4054,22 @@
         <v>4393</v>
       </c>
       <c r="D127" t="n">
-        <v>2800</v>
+        <v>3360</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>2980</v>
       </c>
       <c r="G127" t="n">
-        <v>3370</v>
+        <v>2500</v>
       </c>
       <c r="H127" t="n">
         <v>2500</v>
       </c>
       <c r="I127" t="n">
-        <v>2500</v>
+        <v>1893</v>
       </c>
       <c r="J127" t="n">
-        <v>1893</v>
-      </c>
-      <c r="K127" t="n">
         <v>43.09</v>
       </c>
     </row>
@@ -4341,7 +4096,6 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n"/>
@@ -4357,14 +4111,13 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>7484</v>
+      </c>
       <c r="I129" t="n">
-        <v>7484</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4382,14 +4135,13 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>7110</v>
+      </c>
       <c r="I130" t="n">
-        <v>7110</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4407,14 +4159,13 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>6736</v>
+      </c>
       <c r="I131" t="n">
-        <v>6736</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4432,14 +4183,13 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>5988</v>
+      </c>
       <c r="I132" t="n">
-        <v>5988</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4457,14 +4207,13 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>5239</v>
+      </c>
       <c r="I133" t="n">
-        <v>5239</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4482,14 +4231,13 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>5239</v>
+      </c>
       <c r="I134" t="n">
-        <v>5239</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4516,7 +4264,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Haval F7X / Nissan X-Trail</t>
+          <t>Haval Dargo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4526,17 +4274,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Haval F7 AT</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
           <t xml:space="preserve">Nissan Xtrail </t>
         </is>
       </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n"/>
@@ -4549,27 +4292,24 @@
         <v>7484</v>
       </c>
       <c r="D136" t="n">
+        <v>5760</v>
+      </c>
+      <c r="E136" t="n">
+        <v>10472</v>
+      </c>
+      <c r="F136" t="n">
         <v>4800</v>
       </c>
-      <c r="E136" t="n">
-        <v>9100</v>
-      </c>
-      <c r="F136" t="n">
-        <v>4460</v>
-      </c>
       <c r="G136" t="n">
-        <v>4970</v>
+        <v>3900</v>
       </c>
       <c r="H136" t="n">
         <v>3900</v>
       </c>
       <c r="I136" t="n">
-        <v>3900</v>
+        <v>3584</v>
       </c>
       <c r="J136" t="n">
-        <v>3584</v>
-      </c>
-      <c r="K136" t="n">
         <v>47.89</v>
       </c>
     </row>
@@ -4584,27 +4324,24 @@
         <v>7110</v>
       </c>
       <c r="D137" t="n">
-        <v>4800</v>
+        <v>5760</v>
       </c>
       <c r="E137" t="n">
-        <v>8100</v>
+        <v>8726.67</v>
       </c>
       <c r="F137" t="n">
-        <v>4240</v>
+        <v>4560</v>
       </c>
       <c r="G137" t="n">
-        <v>4670</v>
+        <v>3900</v>
       </c>
       <c r="H137" t="n">
         <v>3900</v>
       </c>
       <c r="I137" t="n">
-        <v>3900</v>
+        <v>3210</v>
       </c>
       <c r="J137" t="n">
-        <v>3210</v>
-      </c>
-      <c r="K137" t="n">
         <v>45.15</v>
       </c>
     </row>
@@ -4619,27 +4356,24 @@
         <v>6736</v>
       </c>
       <c r="D138" t="n">
-        <v>4400</v>
+        <v>5280</v>
       </c>
       <c r="E138" t="n">
-        <v>6250</v>
+        <v>7382.86</v>
       </c>
       <c r="F138" t="n">
-        <v>4020</v>
+        <v>4320</v>
       </c>
       <c r="G138" t="n">
-        <v>4270</v>
+        <v>3700</v>
       </c>
       <c r="H138" t="n">
         <v>3700</v>
       </c>
       <c r="I138" t="n">
-        <v>3700</v>
+        <v>3036</v>
       </c>
       <c r="J138" t="n">
-        <v>3036</v>
-      </c>
-      <c r="K138" t="n">
         <v>45.07</v>
       </c>
     </row>
@@ -4654,27 +4388,24 @@
         <v>5988</v>
       </c>
       <c r="D139" t="n">
-        <v>4400</v>
+        <v>5280</v>
       </c>
       <c r="E139" t="n">
-        <v>5500</v>
+        <v>6387.93</v>
       </c>
       <c r="F139" t="n">
-        <v>4020</v>
+        <v>4320</v>
       </c>
       <c r="G139" t="n">
-        <v>4270</v>
+        <v>3700</v>
       </c>
       <c r="H139" t="n">
         <v>3700</v>
       </c>
       <c r="I139" t="n">
-        <v>3700</v>
+        <v>2288</v>
       </c>
       <c r="J139" t="n">
-        <v>2288</v>
-      </c>
-      <c r="K139" t="n">
         <v>38.21</v>
       </c>
     </row>
@@ -4689,27 +4420,24 @@
         <v>5239</v>
       </c>
       <c r="D140" t="n">
-        <v>4400</v>
+        <v>5280</v>
       </c>
       <c r="E140" t="n">
-        <v>5300</v>
+        <v>5759.62</v>
       </c>
       <c r="F140" t="n">
-        <v>3817.62</v>
+        <v>4080</v>
       </c>
       <c r="G140" t="n">
-        <v>3970</v>
+        <v>2700</v>
       </c>
       <c r="H140" t="n">
         <v>2700</v>
       </c>
       <c r="I140" t="n">
-        <v>2700</v>
+        <v>2539</v>
       </c>
       <c r="J140" t="n">
-        <v>2539</v>
-      </c>
-      <c r="K140" t="n">
         <v>48.46</v>
       </c>
     </row>
@@ -4724,27 +4452,24 @@
         <v>5239</v>
       </c>
       <c r="D141" t="n">
-        <v>3900</v>
+        <v>4680</v>
       </c>
       <c r="E141" t="n">
-        <v>4800</v>
+        <v>5550.17</v>
       </c>
       <c r="F141" t="n">
-        <v>3896.33</v>
+        <v>4080</v>
       </c>
       <c r="G141" t="n">
-        <v>3970</v>
+        <v>2700</v>
       </c>
       <c r="H141" t="n">
         <v>2700</v>
       </c>
       <c r="I141" t="n">
-        <v>2700</v>
+        <v>2539</v>
       </c>
       <c r="J141" t="n">
-        <v>2539</v>
-      </c>
-      <c r="K141" t="n">
         <v>48.46</v>
       </c>
     </row>
@@ -4764,22 +4489,21 @@
           <t>Volkswagen Caravelle T6 Di; Hyundai H-1 II rest. 2</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Hyundai Staria</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>Hyundai H-1 AT</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Hyundai Grand Starex AT</t>
-        </is>
-      </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n"/>
@@ -4791,22 +4515,21 @@
       <c r="C143" t="n">
         <v>6810</v>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="n">
+        <v>11880</v>
+      </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>8080</v>
       </c>
-      <c r="G143" t="n">
-        <v>11270</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>6810</v>
+      </c>
       <c r="I143" t="n">
-        <v>6810</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4820,22 +4543,21 @@
       <c r="C144" t="n">
         <v>6470</v>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="n">
+        <v>11880</v>
+      </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
         <v>7390</v>
       </c>
-      <c r="G144" t="n">
-        <v>10570</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>6470</v>
+      </c>
       <c r="I144" t="n">
-        <v>6470</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4849,22 +4571,21 @@
       <c r="C145" t="n">
         <v>6129</v>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="n">
+        <v>10920</v>
+      </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
         <v>6930</v>
       </c>
-      <c r="G145" t="n">
-        <v>9670</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>6129</v>
+      </c>
       <c r="I145" t="n">
-        <v>6129</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4878,22 +4599,21 @@
       <c r="C146" t="n">
         <v>5448</v>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="n">
+        <v>10920</v>
+      </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
         <v>6930</v>
       </c>
-      <c r="G146" t="n">
-        <v>9670</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>5448</v>
+      </c>
       <c r="I146" t="n">
-        <v>5448</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4907,22 +4627,21 @@
       <c r="C147" t="n">
         <v>4767</v>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="n">
+        <v>10920</v>
+      </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
         <v>6460</v>
       </c>
-      <c r="G147" t="n">
-        <v>9070</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>4767</v>
+      </c>
       <c r="I147" t="n">
-        <v>4767</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4936,22 +4655,21 @@
       <c r="C148" t="n">
         <v>4767</v>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="n">
+        <v>10200</v>
+      </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
         <v>6460</v>
       </c>
-      <c r="G148" t="n">
-        <v>9070</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>4767</v>
+      </c>
       <c r="I148" t="n">
-        <v>4767</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4974,7 +4692,6 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n"/>
@@ -4990,14 +4707,13 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>8512</v>
+      </c>
       <c r="I150" t="n">
-        <v>8512</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5015,14 +4731,13 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="n">
+        <v>8087</v>
+      </c>
       <c r="I151" t="n">
-        <v>8087</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5040,14 +4755,13 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="n">
+        <v>7661</v>
+      </c>
       <c r="I152" t="n">
-        <v>7661</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5065,14 +4779,13 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="n">
+        <v>6810</v>
+      </c>
       <c r="I153" t="n">
-        <v>6810</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5090,14 +4803,13 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="n">
+        <v>5959</v>
+      </c>
       <c r="I154" t="n">
-        <v>5959</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5115,14 +4827,13 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
+      <c r="H155" t="n">
+        <v>5959</v>
+      </c>
       <c r="I155" t="n">
-        <v>5959</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
         <v>0</v>
       </c>
     </row>

--- a/outputs/analysiss.xlsx
+++ b/outputs/analysiss.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="not in the list cars" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-09-2024_@_14_43" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-01-2025_@_13_46" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geely Belgee X50</t>
+          <t>Haval Jolion 2WD</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Haval Jolion 2WD</t>
+          <t>Geely Belgee X50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haval F7X</t>
+          <t>Chery Tiggo 7 Pro Max</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chery Tiggo 7 Pro Max</t>
+          <t>Haval F7X</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gac GS3</t>
+          <t>Haval Jolion 4 WD</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geely Preface </t>
+          <t>Gac GS3</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Geely Preface Flagship</t>
+          <t xml:space="preserve">Geely Preface </t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gac GS8 II</t>
+          <t>Geely Preface Flagship</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zeekr 009</t>
+          <t>Gac GS8 II</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Changan  UNI-K</t>
+          <t>Changan CS 55 PLUS</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Changan CS 55 PLUS</t>
+          <t>Zeekr 009</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Changan UNI-T</t>
+          <t>Changan  UNI-K</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Changan EADO</t>
+          <t>Changan UNI-T</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jaguar XE ВК49865</t>
+          <t>Changan EADO</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zeekr 001</t>
+          <t>Jaguar XE ВК49865</t>
         </is>
       </c>
     </row>
@@ -717,6 +717,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
+        <is>
+          <t>Zeekr 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Lixang Li 9</t>
         </is>
@@ -754,22 +764,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RENT-MOTORS-06-09-24</t>
+          <t>RENT-MOTORS-13-01-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>REX-RENT-06-09-24</t>
+          <t>REX-RENT-13-01-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>A-ARENDA-06-09-24</t>
+          <t>A-ARENDA-13-01-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>STORLET-06-09-24</t>
+          <t>STORLET-13-01-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -805,7 +815,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Renault Logan</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -823,7 +837,9 @@
         <v>2634</v>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>4000</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
@@ -847,7 +863,9 @@
         <v>2503</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>3000</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
@@ -871,7 +889,9 @@
         <v>2371</v>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2714.29</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
@@ -895,7 +915,9 @@
         <v>2187</v>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2607.14</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
@@ -919,7 +941,9 @@
         <v>2055</v>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2571.43</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
@@ -943,7 +967,9 @@
         <v>1976</v>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>2550</v>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
@@ -1630,11 +1656,7 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Hyundai  Solaris 1.6  AT</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>Hyundai Solaris sedan</t>
@@ -1658,20 +1680,18 @@
         <v>3120</v>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>3430</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="H38" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I38" t="n">
-        <v>1576</v>
+        <v>1076</v>
       </c>
       <c r="J38" t="n">
-        <v>44.07</v>
+        <v>30.09</v>
       </c>
     </row>
     <row r="39">
@@ -1688,20 +1708,18 @@
         <v>3120</v>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>3090</v>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="H39" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I39" t="n">
-        <v>1398</v>
+        <v>898</v>
       </c>
       <c r="J39" t="n">
-        <v>41.14</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="40">
@@ -1718,20 +1736,18 @@
         <v>3000</v>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>2950</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="H40" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="I40" t="n">
-        <v>1419</v>
+        <v>819</v>
       </c>
       <c r="J40" t="n">
-        <v>44.08</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="41">
@@ -1748,20 +1764,18 @@
         <v>3000</v>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>2950</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="H41" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="I41" t="n">
-        <v>1169</v>
+        <v>569</v>
       </c>
       <c r="J41" t="n">
-        <v>39.37</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="42">
@@ -1778,20 +1792,18 @@
         <v>3000</v>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>2740</v>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="H42" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="I42" t="n">
-        <v>1290</v>
+        <v>590</v>
       </c>
       <c r="J42" t="n">
-        <v>46.24</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="43">
@@ -1808,20 +1820,18 @@
         <v>2640</v>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>2740</v>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="H43" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="I43" t="n">
-        <v>1182</v>
+        <v>482</v>
       </c>
       <c r="J43" t="n">
-        <v>44.07</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="44">
@@ -2013,7 +2023,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoda Rapid </t>
+          <t>VW Polo sedan</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2034,16 +2044,16 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="H52" t="n">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="I52" t="n">
-        <v>2331</v>
+        <v>1331</v>
       </c>
       <c r="J52" t="n">
-        <v>56.43</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="53">
@@ -2060,16 +2070,16 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="H53" t="n">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="I53" t="n">
-        <v>2125</v>
+        <v>1125</v>
       </c>
       <c r="J53" t="n">
-        <v>54.14</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="54">
@@ -2086,16 +2096,16 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>1600</v>
+        <v>2700</v>
       </c>
       <c r="H54" t="n">
-        <v>1600</v>
+        <v>2700</v>
       </c>
       <c r="I54" t="n">
-        <v>2118</v>
+        <v>1018</v>
       </c>
       <c r="J54" t="n">
-        <v>56.97</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="55">
@@ -2112,16 +2122,16 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>1600</v>
+        <v>2700</v>
       </c>
       <c r="H55" t="n">
-        <v>1600</v>
+        <v>2700</v>
       </c>
       <c r="I55" t="n">
-        <v>1705</v>
+        <v>605</v>
       </c>
       <c r="J55" t="n">
-        <v>51.59</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="56">
@@ -2138,16 +2148,16 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="H56" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="I56" t="n">
-        <v>1492</v>
+        <v>492</v>
       </c>
       <c r="J56" t="n">
-        <v>51.59</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="57">
@@ -2164,16 +2174,16 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="H57" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="I57" t="n">
-        <v>1492</v>
+        <v>492</v>
       </c>
       <c r="J57" t="n">
-        <v>51.59</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="58">
@@ -2224,16 +2234,16 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>3200</v>
+        <v>4800</v>
       </c>
       <c r="H59" t="n">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="I59" t="n">
-        <v>490</v>
+        <v>90</v>
       </c>
       <c r="J59" t="n">
-        <v>13.28</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="60">
@@ -2252,16 +2262,16 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>3200</v>
+        <v>4800</v>
       </c>
       <c r="H60" t="n">
-        <v>3200</v>
+        <v>3506</v>
       </c>
       <c r="I60" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>8.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2280,16 +2290,16 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>2900</v>
+        <v>4500</v>
       </c>
       <c r="H61" t="n">
-        <v>2900</v>
+        <v>3120</v>
       </c>
       <c r="I61" t="n">
-        <v>421</v>
+        <v>201</v>
       </c>
       <c r="J61" t="n">
-        <v>12.68</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="62">
@@ -2308,16 +2318,16 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>2900</v>
+        <v>4500</v>
       </c>
       <c r="H62" t="n">
-        <v>2900</v>
+        <v>2952</v>
       </c>
       <c r="I62" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2336,16 +2346,16 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>2500</v>
+        <v>3800</v>
       </c>
       <c r="H63" t="n">
-        <v>2500</v>
+        <v>2583</v>
       </c>
       <c r="I63" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2364,16 +2374,16 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>2500</v>
+        <v>3800</v>
       </c>
       <c r="H64" t="n">
-        <v>2500</v>
+        <v>2583</v>
       </c>
       <c r="I64" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2401,7 +2411,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kia Ceed</t>
+          <t>Hyundai Elantra NEW</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -2420,20 +2430,20 @@
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>8273</v>
+        <v>8000</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>2200</v>
+        <v>3100</v>
       </c>
       <c r="H66" t="n">
-        <v>2200</v>
+        <v>3100</v>
       </c>
       <c r="I66" t="n">
-        <v>2141</v>
+        <v>1241</v>
       </c>
       <c r="J66" t="n">
-        <v>49.32</v>
+        <v>28.59</v>
       </c>
     </row>
     <row r="67">
@@ -2448,20 +2458,20 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>6702</v>
+        <v>6566.67</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>2200</v>
+        <v>3100</v>
       </c>
       <c r="H67" t="n">
-        <v>2200</v>
+        <v>3100</v>
       </c>
       <c r="I67" t="n">
-        <v>1924</v>
+        <v>1024</v>
       </c>
       <c r="J67" t="n">
-        <v>46.65</v>
+        <v>24.83</v>
       </c>
     </row>
     <row r="68">
@@ -2476,20 +2486,20 @@
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>5969</v>
+        <v>5522.86</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="H68" t="n">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="I68" t="n">
-        <v>1807</v>
+        <v>1107</v>
       </c>
       <c r="J68" t="n">
-        <v>46.25</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="69">
@@ -2504,20 +2514,20 @@
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>5026.57</v>
+        <v>5136.43</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="H69" t="n">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="I69" t="n">
-        <v>1373</v>
+        <v>673</v>
       </c>
       <c r="J69" t="n">
-        <v>39.53</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="70">
@@ -2532,20 +2542,20 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>4817.14</v>
+        <v>4949.05</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="H70" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I70" t="n">
-        <v>1039</v>
+        <v>539</v>
       </c>
       <c r="J70" t="n">
-        <v>34.19</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="71">
@@ -2560,20 +2570,20 @@
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>4293.53</v>
+        <v>4752.67</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="H71" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I71" t="n">
-        <v>1039</v>
+        <v>539</v>
       </c>
       <c r="J71" t="n">
-        <v>34.19</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="72">
@@ -2602,14 +2612,10 @@
           <t>Chery Arrizo 8</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Kia K5</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hyundai i40</t>
+          <t>Mazda 6</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -2630,22 +2636,20 @@
         <v>5160</v>
       </c>
       <c r="E73" t="n">
-        <v>9530</v>
-      </c>
-      <c r="F73" t="n">
-        <v>5000</v>
-      </c>
+        <v>9030</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="H73" t="n">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="I73" t="n">
-        <v>2501</v>
+        <v>1101</v>
       </c>
       <c r="J73" t="n">
-        <v>50.01</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="74">
@@ -2662,22 +2666,20 @@
         <v>5160</v>
       </c>
       <c r="E74" t="n">
-        <v>8482.33</v>
-      </c>
-      <c r="F74" t="n">
-        <v>4750</v>
-      </c>
+        <v>7523.33</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="H74" t="n">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="I74" t="n">
-        <v>2251</v>
+        <v>851</v>
       </c>
       <c r="J74" t="n">
-        <v>47.38</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="75">
@@ -2694,22 +2696,20 @@
         <v>4440</v>
       </c>
       <c r="E75" t="n">
-        <v>6545</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4500</v>
-      </c>
+        <v>6361.43</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="H75" t="n">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="I75" t="n">
-        <v>2101</v>
+        <v>1001</v>
       </c>
       <c r="J75" t="n">
-        <v>46.68</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="76">
@@ -2726,22 +2726,20 @@
         <v>4440</v>
       </c>
       <c r="E76" t="n">
-        <v>5759.57</v>
-      </c>
-      <c r="F76" t="n">
-        <v>4500</v>
-      </c>
+        <v>5930</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="H76" t="n">
-        <v>2400</v>
+        <v>3500</v>
       </c>
       <c r="I76" t="n">
-        <v>1601</v>
+        <v>501</v>
       </c>
       <c r="J76" t="n">
-        <v>40.01</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="77">
@@ -2758,22 +2756,20 @@
         <v>4440</v>
       </c>
       <c r="E77" t="n">
-        <v>5550.14</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4250</v>
-      </c>
+        <v>5710</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>1900</v>
+        <v>2800</v>
       </c>
       <c r="H77" t="n">
-        <v>1900</v>
+        <v>2800</v>
       </c>
       <c r="I77" t="n">
-        <v>1601</v>
+        <v>701</v>
       </c>
       <c r="J77" t="n">
-        <v>45.73</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="78">
@@ -2790,22 +2786,20 @@
         <v>3960</v>
       </c>
       <c r="E78" t="n">
-        <v>5026.57</v>
-      </c>
-      <c r="F78" t="n">
-        <v>4250</v>
-      </c>
+        <v>5497</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>1900</v>
+        <v>2800</v>
       </c>
       <c r="H78" t="n">
-        <v>1900</v>
+        <v>2800</v>
       </c>
       <c r="I78" t="n">
-        <v>1601</v>
+        <v>701</v>
       </c>
       <c r="J78" t="n">
-        <v>45.73</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="79">
@@ -2988,12 +2982,16 @@
           <t>Hyundai CRETA I</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Hyundai Creta</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Renault Kaptur</t>
+          <t>Hyundai Creta</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -3010,20 +3008,22 @@
       <c r="C87" t="n">
         <v>4039</v>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>4050</v>
+      </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="H87" t="n">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="I87" t="n">
-        <v>1839</v>
+        <v>539</v>
       </c>
       <c r="J87" t="n">
-        <v>45.53</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="88">
@@ -3036,20 +3036,22 @@
       <c r="C88" t="n">
         <v>3838</v>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>4050</v>
+      </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="H88" t="n">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="I88" t="n">
-        <v>1638</v>
+        <v>338</v>
       </c>
       <c r="J88" t="n">
-        <v>42.68</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="89">
@@ -3062,20 +3064,22 @@
       <c r="C89" t="n">
         <v>3636</v>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>3600</v>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="H89" t="n">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="I89" t="n">
-        <v>1736</v>
+        <v>536</v>
       </c>
       <c r="J89" t="n">
-        <v>47.74</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="90">
@@ -3088,20 +3092,22 @@
       <c r="C90" t="n">
         <v>3232</v>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>3600</v>
+      </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="H90" t="n">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="I90" t="n">
-        <v>1332</v>
+        <v>132</v>
       </c>
       <c r="J90" t="n">
-        <v>41.21</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="91">
@@ -3114,20 +3120,22 @@
       <c r="C91" t="n">
         <v>3030</v>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>3600</v>
+      </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>1600</v>
+        <v>2800</v>
       </c>
       <c r="H91" t="n">
-        <v>1600</v>
+        <v>2800</v>
       </c>
       <c r="I91" t="n">
-        <v>1430</v>
+        <v>230</v>
       </c>
       <c r="J91" t="n">
-        <v>47.19</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="92">
@@ -3140,20 +3148,22 @@
       <c r="C92" t="n">
         <v>2828</v>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>3300</v>
+      </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>1600</v>
+        <v>2800</v>
       </c>
       <c r="H92" t="n">
-        <v>1600</v>
+        <v>2800</v>
       </c>
       <c r="I92" t="n">
-        <v>1228</v>
+        <v>28</v>
       </c>
       <c r="J92" t="n">
-        <v>43.42</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="93">
@@ -3499,14 +3509,10 @@
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Geely Coolray</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Toyota CH R</t>
+          <t>Changan CS35 PLUS NEW</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -3527,20 +3533,18 @@
         <v>4440</v>
       </c>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="n">
-        <v>3900</v>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>3900</v>
+        <v>4500</v>
       </c>
       <c r="H108" t="n">
-        <v>3900</v>
+        <v>4440</v>
       </c>
       <c r="I108" t="n">
-        <v>801</v>
+        <v>261</v>
       </c>
       <c r="J108" t="n">
-        <v>17.04</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="109">
@@ -3557,20 +3561,18 @@
         <v>4440</v>
       </c>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="n">
-        <v>3700</v>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>3900</v>
+        <v>4500</v>
       </c>
       <c r="H109" t="n">
-        <v>3700</v>
+        <v>4440</v>
       </c>
       <c r="I109" t="n">
-        <v>766</v>
+        <v>26</v>
       </c>
       <c r="J109" t="n">
-        <v>17.15</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="110">
@@ -3587,20 +3589,18 @@
         <v>3960</v>
       </c>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="n">
-        <v>3510</v>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>3500</v>
+        <v>4100</v>
       </c>
       <c r="H110" t="n">
-        <v>3500</v>
+        <v>3960</v>
       </c>
       <c r="I110" t="n">
-        <v>731</v>
+        <v>271</v>
       </c>
       <c r="J110" t="n">
-        <v>17.28</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="111">
@@ -3617,20 +3617,18 @@
         <v>3960</v>
       </c>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="n">
-        <v>3510</v>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>3500</v>
+        <v>4100</v>
       </c>
       <c r="H111" t="n">
-        <v>3500</v>
+        <v>3761</v>
       </c>
       <c r="I111" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3647,20 +3645,18 @@
         <v>3960</v>
       </c>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="n">
-        <v>3310</v>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="H112" t="n">
-        <v>2500</v>
+        <v>3291</v>
       </c>
       <c r="I112" t="n">
-        <v>791</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>24.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3677,20 +3673,18 @@
         <v>3360</v>
       </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="n">
-        <v>3310</v>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="H113" t="n">
-        <v>2500</v>
+        <v>3291</v>
       </c>
       <c r="I113" t="n">
-        <v>791</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>24.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3881,12 +3875,12 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haval M6 </t>
+          <t>Haval Jolion</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Kia Sportage SLS</t>
+          <t>Hyundai Tucson</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -3904,23 +3898,23 @@
         <v>6275</v>
       </c>
       <c r="D122" t="n">
-        <v>4560</v>
+        <v>5560</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>3500</v>
+        <v>3150</v>
       </c>
       <c r="G122" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="H122" t="n">
-        <v>3500</v>
+        <v>3150</v>
       </c>
       <c r="I122" t="n">
-        <v>2775</v>
+        <v>3125</v>
       </c>
       <c r="J122" t="n">
-        <v>44.22</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="123">
@@ -3934,23 +3928,23 @@
         <v>5962</v>
       </c>
       <c r="D123" t="n">
-        <v>4560</v>
+        <v>5560</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>3330</v>
+        <v>3150</v>
       </c>
       <c r="G123" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="H123" t="n">
-        <v>3330</v>
+        <v>3150</v>
       </c>
       <c r="I123" t="n">
-        <v>2632</v>
+        <v>2812</v>
       </c>
       <c r="J123" t="n">
-        <v>44.15</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="124">
@@ -3964,14 +3958,14 @@
         <v>5648</v>
       </c>
       <c r="D124" t="n">
-        <v>3960</v>
+        <v>4960</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>3150</v>
       </c>
       <c r="G124" t="n">
-        <v>3300</v>
+        <v>4400</v>
       </c>
       <c r="H124" t="n">
         <v>3150</v>
@@ -3994,14 +3988,14 @@
         <v>5020</v>
       </c>
       <c r="D125" t="n">
-        <v>3960</v>
+        <v>4960</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>3150</v>
       </c>
       <c r="G125" t="n">
-        <v>3300</v>
+        <v>4400</v>
       </c>
       <c r="H125" t="n">
         <v>3150</v>
@@ -4024,23 +4018,23 @@
         <v>4393</v>
       </c>
       <c r="D126" t="n">
-        <v>3960</v>
+        <v>4960</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
         <v>2980</v>
       </c>
       <c r="G126" t="n">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="H126" t="n">
-        <v>2500</v>
+        <v>2980</v>
       </c>
       <c r="I126" t="n">
-        <v>1893</v>
+        <v>1413</v>
       </c>
       <c r="J126" t="n">
-        <v>43.09</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="127">
@@ -4054,23 +4048,23 @@
         <v>4393</v>
       </c>
       <c r="D127" t="n">
-        <v>3360</v>
+        <v>4360</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
         <v>2980</v>
       </c>
       <c r="G127" t="n">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="H127" t="n">
-        <v>2500</v>
+        <v>2980</v>
       </c>
       <c r="I127" t="n">
-        <v>1893</v>
+        <v>1413</v>
       </c>
       <c r="J127" t="n">
-        <v>43.09</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="128">
@@ -4257,11 +4251,7 @@
           <t>Nissan X-Trail III rest.</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Nissan X-Trail</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>Haval Dargo</t>
@@ -4269,7 +4259,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Haval F7X  4WD</t>
+          <t>Haval Dargo 4WD</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -4291,26 +4281,24 @@
       <c r="C136" t="n">
         <v>7484</v>
       </c>
-      <c r="D136" t="n">
-        <v>5760</v>
-      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>10472</v>
+        <v>12020</v>
       </c>
       <c r="F136" t="n">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="G136" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="H136" t="n">
-        <v>3900</v>
+        <v>4500</v>
       </c>
       <c r="I136" t="n">
-        <v>3584</v>
+        <v>2984</v>
       </c>
       <c r="J136" t="n">
-        <v>47.89</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="137">
@@ -4323,26 +4311,24 @@
       <c r="C137" t="n">
         <v>7110</v>
       </c>
-      <c r="D137" t="n">
-        <v>5760</v>
-      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>8726.67</v>
+        <v>9186.67</v>
       </c>
       <c r="F137" t="n">
-        <v>4560</v>
+        <v>4500</v>
       </c>
       <c r="G137" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="H137" t="n">
-        <v>3900</v>
+        <v>4500</v>
       </c>
       <c r="I137" t="n">
-        <v>3210</v>
+        <v>2610</v>
       </c>
       <c r="J137" t="n">
-        <v>45.15</v>
+        <v>36.71</v>
       </c>
     </row>
     <row r="138">
@@ -4355,26 +4341,24 @@
       <c r="C138" t="n">
         <v>6736</v>
       </c>
-      <c r="D138" t="n">
-        <v>5280</v>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
-        <v>7382.86</v>
+        <v>7575.71</v>
       </c>
       <c r="F138" t="n">
-        <v>4320</v>
+        <v>4500</v>
       </c>
       <c r="G138" t="n">
-        <v>3700</v>
+        <v>5100</v>
       </c>
       <c r="H138" t="n">
-        <v>3700</v>
+        <v>4500</v>
       </c>
       <c r="I138" t="n">
-        <v>3036</v>
+        <v>2236</v>
       </c>
       <c r="J138" t="n">
-        <v>45.07</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="139">
@@ -4387,26 +4371,24 @@
       <c r="C139" t="n">
         <v>5988</v>
       </c>
-      <c r="D139" t="n">
-        <v>5280</v>
-      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
-        <v>6387.93</v>
+        <v>6370</v>
       </c>
       <c r="F139" t="n">
-        <v>4320</v>
+        <v>4500</v>
       </c>
       <c r="G139" t="n">
-        <v>3700</v>
+        <v>5100</v>
       </c>
       <c r="H139" t="n">
-        <v>3700</v>
+        <v>4500</v>
       </c>
       <c r="I139" t="n">
-        <v>2288</v>
+        <v>1488</v>
       </c>
       <c r="J139" t="n">
-        <v>38.21</v>
+        <v>24.85</v>
       </c>
     </row>
     <row r="140">
@@ -4419,26 +4401,24 @@
       <c r="C140" t="n">
         <v>5239</v>
       </c>
-      <c r="D140" t="n">
-        <v>5280</v>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>5759.62</v>
+        <v>6134.76</v>
       </c>
       <c r="F140" t="n">
-        <v>4080</v>
+        <v>4250</v>
       </c>
       <c r="G140" t="n">
-        <v>2700</v>
+        <v>4800</v>
       </c>
       <c r="H140" t="n">
-        <v>2700</v>
+        <v>4250</v>
       </c>
       <c r="I140" t="n">
-        <v>2539</v>
+        <v>989</v>
       </c>
       <c r="J140" t="n">
-        <v>48.46</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="141">
@@ -4451,26 +4431,24 @@
       <c r="C141" t="n">
         <v>5239</v>
       </c>
-      <c r="D141" t="n">
-        <v>4680</v>
-      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>5550.17</v>
+        <v>5898</v>
       </c>
       <c r="F141" t="n">
-        <v>4080</v>
+        <v>4250</v>
       </c>
       <c r="G141" t="n">
-        <v>2700</v>
+        <v>4800</v>
       </c>
       <c r="H141" t="n">
-        <v>2700</v>
+        <v>4250</v>
       </c>
       <c r="I141" t="n">
-        <v>2539</v>
+        <v>989</v>
       </c>
       <c r="J141" t="n">
-        <v>48.46</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="142">

--- a/outputs/analysiss.xlsx
+++ b/outputs/analysiss.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="not in the list cars" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-01-2025_@_13_46" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-03-2025_@_00_37" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -764,22 +764,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RENT-MOTORS-13-01-25</t>
+          <t>RENT-MOTORS-04-03-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>REX-RENT-13-01-25</t>
+          <t>REX-RENT-04-03-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>A-ARENDA-13-01-25</t>
+          <t>A-ARENDA-04-03-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>STORLET-13-01-25</t>
+          <t>STORLET-04-03-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -814,12 +814,12 @@
           <t>Volkswagen Polo V</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Renault Logan</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -836,20 +836,20 @@
       <c r="C3" t="n">
         <v>2634</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>4000</v>
-      </c>
+      <c r="D3" t="n">
+        <v>2350</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2634</v>
+        <v>2350</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="4">
@@ -862,20 +862,20 @@
       <c r="C4" t="n">
         <v>2503</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>3000</v>
-      </c>
+      <c r="D4" t="n">
+        <v>2350</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>2503</v>
+        <v>2350</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="5">
@@ -888,20 +888,20 @@
       <c r="C5" t="n">
         <v>2371</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>2714.29</v>
-      </c>
+      <c r="D5" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2371</v>
+        <v>1950</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="6">
@@ -914,20 +914,20 @@
       <c r="C6" t="n">
         <v>2187</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>2607.14</v>
-      </c>
+      <c r="D6" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2187</v>
+        <v>1950</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="7">
@@ -940,20 +940,20 @@
       <c r="C7" t="n">
         <v>2055</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>2571.43</v>
-      </c>
+      <c r="D7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>2055</v>
+        <v>1950</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="8">
@@ -966,20 +966,20 @@
       <c r="C8" t="n">
         <v>1976</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>2550</v>
-      </c>
+      <c r="D8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1976</v>
+        <v>1450</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="9">
@@ -1677,7 +1677,7 @@
         <v>3576</v>
       </c>
       <c r="D38" t="n">
-        <v>3120</v>
+        <v>2600</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
         <v>3398</v>
       </c>
       <c r="D39" t="n">
-        <v>3120</v>
+        <v>2600</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -1733,7 +1733,7 @@
         <v>3219</v>
       </c>
       <c r="D40" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1761,7 +1761,7 @@
         <v>2969</v>
       </c>
       <c r="D41" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>2790</v>
       </c>
       <c r="D42" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
         <v>2682</v>
       </c>
       <c r="D43" t="n">
-        <v>2640</v>
+        <v>2200</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         <v>3690</v>
       </c>
       <c r="D59" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -2237,13 +2237,13 @@
         <v>4800</v>
       </c>
       <c r="H59" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="I59" t="n">
-        <v>90</v>
+        <v>690</v>
       </c>
       <c r="J59" t="n">
-        <v>2.44</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="60">
@@ -2257,7 +2257,7 @@
         <v>3506</v>
       </c>
       <c r="D60" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -2265,13 +2265,13 @@
         <v>4800</v>
       </c>
       <c r="H60" t="n">
-        <v>3506</v>
+        <v>3000</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="61">
@@ -2285,7 +2285,7 @@
         <v>3321</v>
       </c>
       <c r="D61" t="n">
-        <v>3120</v>
+        <v>2600</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
@@ -2293,13 +2293,13 @@
         <v>4500</v>
       </c>
       <c r="H61" t="n">
-        <v>3120</v>
+        <v>2600</v>
       </c>
       <c r="I61" t="n">
-        <v>201</v>
+        <v>721</v>
       </c>
       <c r="J61" t="n">
-        <v>6.05</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="62">
@@ -2313,7 +2313,7 @@
         <v>2952</v>
       </c>
       <c r="D62" t="n">
-        <v>3120</v>
+        <v>2600</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -2321,13 +2321,13 @@
         <v>4500</v>
       </c>
       <c r="H62" t="n">
-        <v>2952</v>
+        <v>2600</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="63">
@@ -2341,7 +2341,7 @@
         <v>2583</v>
       </c>
       <c r="D63" t="n">
-        <v>3120</v>
+        <v>2600</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
         <v>2583</v>
       </c>
       <c r="D64" t="n">
-        <v>2880</v>
+        <v>2400</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -2377,13 +2377,13 @@
         <v>3800</v>
       </c>
       <c r="H64" t="n">
-        <v>2583</v>
+        <v>2400</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="65">
@@ -2633,7 +2633,7 @@
         <v>5001</v>
       </c>
       <c r="D73" t="n">
-        <v>5160</v>
+        <v>4300</v>
       </c>
       <c r="E73" t="n">
         <v>9030</v>
@@ -2663,7 +2663,7 @@
         <v>4751</v>
       </c>
       <c r="D74" t="n">
-        <v>5160</v>
+        <v>4300</v>
       </c>
       <c r="E74" t="n">
         <v>7523.33</v>
@@ -2693,7 +2693,7 @@
         <v>4501</v>
       </c>
       <c r="D75" t="n">
-        <v>4440</v>
+        <v>3700</v>
       </c>
       <c r="E75" t="n">
         <v>6361.43</v>
@@ -2723,7 +2723,7 @@
         <v>4001</v>
       </c>
       <c r="D76" t="n">
-        <v>4440</v>
+        <v>3700</v>
       </c>
       <c r="E76" t="n">
         <v>5930</v>
@@ -2753,7 +2753,7 @@
         <v>3501</v>
       </c>
       <c r="D77" t="n">
-        <v>4440</v>
+        <v>3700</v>
       </c>
       <c r="E77" t="n">
         <v>5710</v>
@@ -2783,7 +2783,7 @@
         <v>3501</v>
       </c>
       <c r="D78" t="n">
-        <v>3960</v>
+        <v>3300</v>
       </c>
       <c r="E78" t="n">
         <v>5497</v>
@@ -3009,7 +3009,7 @@
         <v>4039</v>
       </c>
       <c r="D87" t="n">
-        <v>4050</v>
+        <v>3100</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
@@ -3017,13 +3017,13 @@
         <v>3500</v>
       </c>
       <c r="H87" t="n">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="I87" t="n">
-        <v>539</v>
+        <v>939</v>
       </c>
       <c r="J87" t="n">
-        <v>13.34</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="88">
@@ -3037,7 +3037,7 @@
         <v>3838</v>
       </c>
       <c r="D88" t="n">
-        <v>4050</v>
+        <v>3100</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
@@ -3045,13 +3045,13 @@
         <v>3500</v>
       </c>
       <c r="H88" t="n">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="I88" t="n">
-        <v>338</v>
+        <v>738</v>
       </c>
       <c r="J88" t="n">
-        <v>8.81</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="89">
@@ -3065,7 +3065,7 @@
         <v>3636</v>
       </c>
       <c r="D89" t="n">
-        <v>3600</v>
+        <v>2800</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
@@ -3073,13 +3073,13 @@
         <v>3100</v>
       </c>
       <c r="H89" t="n">
-        <v>3100</v>
+        <v>2800</v>
       </c>
       <c r="I89" t="n">
-        <v>536</v>
+        <v>836</v>
       </c>
       <c r="J89" t="n">
-        <v>14.74</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="90">
@@ -3093,7 +3093,7 @@
         <v>3232</v>
       </c>
       <c r="D90" t="n">
-        <v>3600</v>
+        <v>2800</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -3101,13 +3101,13 @@
         <v>3100</v>
       </c>
       <c r="H90" t="n">
-        <v>3100</v>
+        <v>2800</v>
       </c>
       <c r="I90" t="n">
-        <v>132</v>
+        <v>432</v>
       </c>
       <c r="J90" t="n">
-        <v>4.08</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="91">
@@ -3121,7 +3121,7 @@
         <v>3030</v>
       </c>
       <c r="D91" t="n">
-        <v>3600</v>
+        <v>2800</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -3149,7 +3149,7 @@
         <v>2828</v>
       </c>
       <c r="D92" t="n">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
@@ -3157,13 +3157,13 @@
         <v>2800</v>
       </c>
       <c r="H92" t="n">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="I92" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="J92" t="n">
-        <v>0.99</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="93">
@@ -3183,7 +3183,11 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Сhery Tiggo 4</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -3201,7 +3205,9 @@
         <v>4487</v>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="n">
+        <v>6050</v>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
@@ -3225,7 +3231,9 @@
         <v>4263</v>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>4750</v>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
@@ -3249,17 +3257,19 @@
         <v>4039</v>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>3934.29</v>
+      </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>4039</v>
+        <v>3934.29</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>104.71</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="97">
@@ -3273,7 +3283,9 @@
         <v>3590</v>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="n">
+        <v>3630.71</v>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
@@ -3297,7 +3309,9 @@
         <v>3366</v>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>3519.05</v>
+      </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
@@ -3321,7 +3335,9 @@
         <v>3141</v>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>3380.33</v>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
@@ -3530,7 +3546,7 @@
         <v>4701</v>
       </c>
       <c r="D108" t="n">
-        <v>4440</v>
+        <v>3500</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
@@ -3538,13 +3554,13 @@
         <v>4500</v>
       </c>
       <c r="H108" t="n">
-        <v>4440</v>
+        <v>3500</v>
       </c>
       <c r="I108" t="n">
-        <v>261</v>
+        <v>1201</v>
       </c>
       <c r="J108" t="n">
-        <v>5.55</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="109">
@@ -3558,7 +3574,7 @@
         <v>4466</v>
       </c>
       <c r="D109" t="n">
-        <v>4440</v>
+        <v>3500</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
@@ -3566,13 +3582,13 @@
         <v>4500</v>
       </c>
       <c r="H109" t="n">
-        <v>4440</v>
+        <v>3500</v>
       </c>
       <c r="I109" t="n">
-        <v>26</v>
+        <v>966</v>
       </c>
       <c r="J109" t="n">
-        <v>0.58</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="110">
@@ -3586,7 +3602,7 @@
         <v>4231</v>
       </c>
       <c r="D110" t="n">
-        <v>3960</v>
+        <v>2970</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
@@ -3594,13 +3610,13 @@
         <v>4100</v>
       </c>
       <c r="H110" t="n">
-        <v>3960</v>
+        <v>2970</v>
       </c>
       <c r="I110" t="n">
-        <v>271</v>
+        <v>1261</v>
       </c>
       <c r="J110" t="n">
-        <v>6.41</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="111">
@@ -3614,7 +3630,7 @@
         <v>3761</v>
       </c>
       <c r="D111" t="n">
-        <v>3960</v>
+        <v>2970</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
@@ -3622,13 +3638,13 @@
         <v>4100</v>
       </c>
       <c r="H111" t="n">
-        <v>3761</v>
+        <v>2970</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>791</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="112">
@@ -3642,7 +3658,7 @@
         <v>3291</v>
       </c>
       <c r="D112" t="n">
-        <v>3960</v>
+        <v>2970</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
@@ -3650,13 +3666,13 @@
         <v>3600</v>
       </c>
       <c r="H112" t="n">
-        <v>3291</v>
+        <v>2970</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="113">
@@ -3670,7 +3686,7 @@
         <v>3291</v>
       </c>
       <c r="D113" t="n">
-        <v>3360</v>
+        <v>2800</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
@@ -3678,13 +3694,13 @@
         <v>3600</v>
       </c>
       <c r="H113" t="n">
-        <v>3291</v>
+        <v>2800</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="114">
@@ -3898,7 +3914,7 @@
         <v>6275</v>
       </c>
       <c r="D122" t="n">
-        <v>5560</v>
+        <v>3800</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
@@ -3928,7 +3944,7 @@
         <v>5962</v>
       </c>
       <c r="D123" t="n">
-        <v>5560</v>
+        <v>3800</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
@@ -3958,7 +3974,7 @@
         <v>5648</v>
       </c>
       <c r="D124" t="n">
-        <v>4960</v>
+        <v>3300</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
@@ -3988,7 +4004,7 @@
         <v>5020</v>
       </c>
       <c r="D125" t="n">
-        <v>4960</v>
+        <v>3300</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
@@ -4018,7 +4034,7 @@
         <v>4393</v>
       </c>
       <c r="D126" t="n">
-        <v>4960</v>
+        <v>3300</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
@@ -4048,23 +4064,23 @@
         <v>4393</v>
       </c>
       <c r="D127" t="n">
-        <v>4360</v>
+        <v>2800</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>2980</v>
+        <v>3082.67</v>
       </c>
       <c r="G127" t="n">
         <v>3300</v>
       </c>
       <c r="H127" t="n">
-        <v>2980</v>
+        <v>2800</v>
       </c>
       <c r="I127" t="n">
-        <v>1413</v>
+        <v>1593</v>
       </c>
       <c r="J127" t="n">
-        <v>32.16</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="128">
@@ -4252,11 +4268,7 @@
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Haval Dargo</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>Haval Dargo 4WD</t>
@@ -4282,9 +4294,7 @@
         <v>7484</v>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="n">
-        <v>12020</v>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>4500</v>
       </c>
@@ -4312,9 +4322,7 @@
         <v>7110</v>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="n">
-        <v>9186.67</v>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="n">
         <v>4500</v>
       </c>
@@ -4342,9 +4350,7 @@
         <v>6736</v>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="n">
-        <v>7575.71</v>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
         <v>4500</v>
       </c>
@@ -4372,9 +4378,7 @@
         <v>5988</v>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="n">
-        <v>6370</v>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
         <v>4500</v>
       </c>
@@ -4402,9 +4406,7 @@
         <v>5239</v>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="n">
-        <v>6134.76</v>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
         <v>4250</v>
       </c>
@@ -4432,23 +4434,21 @@
         <v>5239</v>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="n">
-        <v>5898</v>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
-        <v>4250</v>
+        <v>4399.33</v>
       </c>
       <c r="G141" t="n">
         <v>4800</v>
       </c>
       <c r="H141" t="n">
-        <v>4250</v>
+        <v>4399.33</v>
       </c>
       <c r="I141" t="n">
-        <v>989</v>
+        <v>839.6700000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>18.88</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="142">
@@ -4475,7 +4475,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hyundai H-1 AT</t>
+          <t>Hyundai Palisade HT</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -4494,11 +4494,11 @@
         <v>6810</v>
       </c>
       <c r="D143" t="n">
-        <v>11880</v>
+        <v>9900</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>8080</v>
+        <v>11000</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
@@ -4522,11 +4522,11 @@
         <v>6470</v>
       </c>
       <c r="D144" t="n">
-        <v>11880</v>
+        <v>9900</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>7390</v>
+        <v>9900</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
@@ -4550,11 +4550,11 @@
         <v>6129</v>
       </c>
       <c r="D145" t="n">
-        <v>10920</v>
+        <v>9100</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>6930</v>
+        <v>9350</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
@@ -4578,11 +4578,11 @@
         <v>5448</v>
       </c>
       <c r="D146" t="n">
-        <v>10920</v>
+        <v>9100</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>6930</v>
+        <v>9350</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
@@ -4606,11 +4606,11 @@
         <v>4767</v>
       </c>
       <c r="D147" t="n">
-        <v>10920</v>
+        <v>9100</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="n">
-        <v>6460</v>
+        <v>8800</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
@@ -4634,11 +4634,11 @@
         <v>4767</v>
       </c>
       <c r="D148" t="n">
-        <v>10200</v>
+        <v>8500</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="n">
-        <v>6460</v>
+        <v>8800</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
